--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54,6 +54,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -510,7 +578,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -588,7 +656,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -666,7 +734,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -744,7 +812,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -822,7 +890,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -900,7 +968,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -978,7 +1046,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1124,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1202,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1280,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1358,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1436,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1514,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1592,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1670,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1748,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1826,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1904,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1982,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1992,7 +2060,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2138,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2216,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2294,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2372,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2450,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2528,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2606,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2684,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2762,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2840,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2918,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2996,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3074,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3152,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3230,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3308,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3386,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3464,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3542,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3620,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3698,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3776,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3854,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3932,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3942,7 +4010,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4088,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4166,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4244,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4322,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4400,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4478,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4556,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4634,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4712,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4790,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4868,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4946,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4956,7 +5024,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5102,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5180,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5258,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5336,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5414,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5492,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5570,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5645,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5720,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5727,7 +5795,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5870,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5945,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5952,7 +6020,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6027,7 +6095,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6170,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6177,7 +6245,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6320,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6327,7 +6395,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6470,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6477,7 +6545,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6620,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6695,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6773,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6851,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6929,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6936,7 +7004,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7011,7 +7079,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7086,7 +7154,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7232,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7307,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7385,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7463,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7541,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7619,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7629,7 +7697,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7707,7 +7775,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7853,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7928,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7938,7 +8006,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8084,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8162,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8240,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8315,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8390,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8543,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8550,7 +8618,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8625,7 +8693,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8768,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8775,7 +8843,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8918,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8993,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9000,7 +9068,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9143,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9218,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9293,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9368,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9375,7 +9443,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9518,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9528,7 +9596,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9603,7 +9671,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9678,7 +9746,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9824,7 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9902,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9912,7 +9980,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9990,7 +10058,7 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10136,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10214,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10292,7 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10299,7 +10367,7 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10374,7 +10442,7 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10449,7 +10517,7 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10524,7 +10592,7 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10667,7 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10667,6 +10735,9 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
+      <c r="N134" t="n">
+        <v>0.666</v>
+      </c>
       <c r="O134" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10674,12 +10745,7 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q134" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10754,12 +10820,7 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10834,12 +10895,7 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10914,12 +10970,7 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10994,12 +11045,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11067,6 +11113,9 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
+      <c r="N139" t="n">
+        <v>0.8149999999999999</v>
+      </c>
       <c r="O139" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -11074,12 +11123,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11154,12 +11198,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q140" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11234,12 +11273,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q141" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11314,12 +11348,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11394,12 +11423,7 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q143" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11467,6 +11491,9 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
+      <c r="N144" t="n">
+        <v>0.883</v>
+      </c>
       <c r="O144" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -11474,12 +11501,7 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q144" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11554,12 +11576,7 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11634,12 +11651,7 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q146" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11714,12 +11726,7 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q147" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11787,6 +11794,9 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
+      <c r="N148" t="n">
+        <v>0.904</v>
+      </c>
       <c r="O148" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -11794,12 +11804,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11867,6 +11872,9 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
+      <c r="N149" t="n">
+        <v>0.904</v>
+      </c>
       <c r="O149" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -11874,12 +11882,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11947,6 +11950,9 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
+      <c r="N150" t="n">
+        <v>0.904</v>
+      </c>
       <c r="O150" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -11954,12 +11960,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12034,12 +12035,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12114,12 +12110,7 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12194,12 +12185,7 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12267,6 +12253,9 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
+      <c r="N154" t="n">
+        <v>0.83</v>
+      </c>
       <c r="O154" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12274,12 +12263,7 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12347,6 +12331,9 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
+      <c r="N155" t="n">
+        <v>0.996</v>
+      </c>
       <c r="O155" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12354,12 +12341,7 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12427,6 +12409,9 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
+      <c r="N156" t="n">
+        <v>0.833</v>
+      </c>
       <c r="O156" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12434,12 +12419,7 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12514,12 +12494,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q157" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12587,6 +12562,9 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
+      <c r="N158" t="n">
+        <v>1.436</v>
+      </c>
       <c r="O158" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12594,12 +12572,7 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q158" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12667,6 +12640,9 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
+      <c r="N159" t="n">
+        <v>1.196</v>
+      </c>
       <c r="O159" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12674,12 +12650,7 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q159" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12747,6 +12718,9 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
+      <c r="N160" t="n">
+        <v>1.399</v>
+      </c>
       <c r="O160" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12754,12 +12728,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q160" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12827,6 +12796,9 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
+      <c r="N161" t="n">
+        <v>1.401</v>
+      </c>
       <c r="O161" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12834,12 +12806,7 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12907,6 +12874,9 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
+      <c r="N162" t="n">
+        <v>1.6</v>
+      </c>
       <c r="O162" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12914,12 +12884,7 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12987,6 +12952,9 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
+      <c r="N163" t="n">
+        <v>1.695</v>
+      </c>
       <c r="O163" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -12994,12 +12962,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13067,6 +13030,9 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
+      <c r="N164" t="n">
+        <v>1.564</v>
+      </c>
       <c r="O164" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13074,12 +13040,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q164" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13154,12 +13115,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q165" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13234,12 +13190,7 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13314,12 +13265,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13394,12 +13340,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13467,6 +13408,9 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
+      <c r="N169" t="n">
+        <v>1.94</v>
+      </c>
       <c r="O169" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13474,12 +13418,7 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13554,12 +13493,7 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q170" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13634,12 +13568,7 @@
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13714,12 +13643,7 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13794,12 +13718,7 @@
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q173" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13874,12 +13793,7 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13947,6 +13861,9 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
+      <c r="N175" t="n">
+        <v>1.922</v>
+      </c>
       <c r="O175" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13954,12 +13871,7 @@
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q175" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14034,12 +13946,7 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q176" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14114,12 +14021,7 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q177" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14194,12 +14096,7 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14274,12 +14171,7 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q179" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14354,12 +14246,7 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q180" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14434,12 +14321,7 @@
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q181" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14514,12 +14396,7 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q182" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14594,12 +14471,7 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q183" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14674,12 +14546,7 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14754,12 +14621,7 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q185" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14834,12 +14696,7 @@
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q186" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14914,12 +14771,7 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q187" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14994,12 +14846,7 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q188" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15074,12 +14921,7 @@
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q189" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15154,12 +14996,7 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q190" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15227,6 +15064,9 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
+      <c r="N191" t="n">
+        <v>1.664</v>
+      </c>
       <c r="O191" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -15234,12 +15074,7 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q191" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15314,12 +15149,7 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q192" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15394,12 +15224,7 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q193" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15474,12 +15299,7 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q194" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15554,12 +15374,7 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q195" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15634,12 +15449,7 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q196" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15714,12 +15524,7 @@
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q197" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15794,12 +15599,7 @@
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15874,12 +15674,7 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="Q199" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15915,7 +15710,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>2026</v>
+        <v>1960</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -15929,22 +15724,22 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Sistema sanitario</t>
+          <t>Mortalidad</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>sistema_sanitario</t>
+          <t>mortalidad</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>SH.MED.PHYS.ZS</t>
+          <t>SH.STA.MMRT</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Médicos por cada 1.000 habitantes</t>
+          <t>Mortalidad materna</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -15954,7 +15749,7 @@
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
@@ -15995,7 +15790,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -16034,7 +15829,12 @@
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -16070,7 +15870,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -16109,7 +15909,12 @@
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -16145,7 +15950,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -16184,7 +15989,12 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -16220,7 +16030,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -16259,7 +16069,12 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -16295,7 +16110,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -16334,7 +16149,12 @@
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -16370,7 +16190,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -16409,7 +16229,12 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -16445,7 +16270,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -16484,7 +16309,12 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -16520,7 +16350,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -16559,7 +16389,12 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -16595,7 +16430,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -16634,7 +16469,12 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -16670,7 +16510,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -16709,7 +16549,12 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -16745,7 +16590,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -16784,7 +16629,12 @@
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -16820,7 +16670,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -16859,7 +16709,12 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -16895,7 +16750,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -16934,7 +16789,12 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -16970,7 +16830,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -17009,7 +16869,12 @@
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -17045,7 +16910,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -17084,7 +16949,12 @@
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -17120,7 +16990,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -17159,7 +17029,12 @@
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -17195,7 +17070,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -17234,7 +17109,12 @@
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -17270,7 +17150,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -17309,7 +17189,12 @@
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17230,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -17384,7 +17269,12 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -17420,7 +17310,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -17459,7 +17349,12 @@
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -17495,7 +17390,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -17534,7 +17429,12 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -17570,7 +17470,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -17609,7 +17509,12 @@
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -17645,7 +17550,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -17684,7 +17589,12 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -17720,7 +17630,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -17759,7 +17669,12 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -17795,7 +17710,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -17834,7 +17749,12 @@
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -17870,7 +17790,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -17902,9 +17822,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N226" t="n">
-        <v>83</v>
-      </c>
       <c r="O226" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17912,7 +17829,12 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -17948,7 +17870,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -17980,9 +17902,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N227" t="n">
-        <v>81</v>
-      </c>
       <c r="O227" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17990,7 +17909,12 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -18026,7 +17950,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -18058,9 +17982,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N228" t="n">
-        <v>81</v>
-      </c>
       <c r="O228" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18068,7 +17989,12 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -18104,7 +18030,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -18136,9 +18062,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N229" t="n">
-        <v>80</v>
-      </c>
       <c r="O229" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18146,7 +18069,12 @@
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -18182,7 +18110,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -18214,9 +18142,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N230" t="n">
-        <v>80</v>
-      </c>
       <c r="O230" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18224,7 +18149,12 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -18260,7 +18190,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -18292,9 +18222,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N231" t="n">
-        <v>83</v>
-      </c>
       <c r="O231" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18302,7 +18229,12 @@
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -18338,7 +18270,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -18370,9 +18302,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N232" t="n">
-        <v>80</v>
-      </c>
       <c r="O232" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18380,7 +18309,12 @@
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -18416,7 +18350,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -18448,9 +18382,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N233" t="n">
-        <v>82</v>
-      </c>
       <c r="O233" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18458,7 +18389,12 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -18494,7 +18430,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -18526,9 +18462,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N234" t="n">
-        <v>82</v>
-      </c>
       <c r="O234" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18536,7 +18469,12 @@
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -18572,7 +18510,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -18604,9 +18542,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N235" t="n">
-        <v>84</v>
-      </c>
       <c r="O235" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18614,7 +18549,12 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -18650,7 +18590,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -18682,9 +18622,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N236" t="n">
-        <v>84</v>
-      </c>
       <c r="O236" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18692,7 +18629,12 @@
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -18728,7 +18670,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -18760,9 +18702,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N237" t="n">
-        <v>86</v>
-      </c>
       <c r="O237" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18770,7 +18709,12 @@
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -18806,7 +18750,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -18838,9 +18782,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N238" t="n">
-        <v>82</v>
-      </c>
       <c r="O238" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18848,7 +18789,12 @@
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -18884,7 +18830,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -18916,9 +18862,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N239" t="n">
-        <v>82</v>
-      </c>
       <c r="O239" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18926,7 +18869,12 @@
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -18962,7 +18910,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -18994,9 +18942,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N240" t="n">
-        <v>88</v>
-      </c>
       <c r="O240" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19004,7 +18949,12 @@
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -19040,7 +18990,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -19072,9 +19022,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N241" t="n">
-        <v>86</v>
-      </c>
       <c r="O241" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19082,7 +19029,12 @@
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -19118,7 +19070,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -19150,9 +19102,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N242" t="n">
-        <v>101</v>
-      </c>
       <c r="O242" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19160,7 +19109,12 @@
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -19196,7 +19150,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -19228,9 +19182,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N243" t="n">
-        <v>87</v>
-      </c>
       <c r="O243" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19238,7 +19189,12 @@
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -19274,7 +19230,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -19306,9 +19262,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N244" t="n">
-        <v>97</v>
-      </c>
       <c r="O244" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19316,7 +19269,12 @@
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -19352,7 +19310,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -19384,9 +19342,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N245" t="n">
-        <v>94</v>
-      </c>
       <c r="O245" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19394,7 +19349,12 @@
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -19430,7 +19390,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -19462,9 +19422,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N246" t="n">
-        <v>93</v>
-      </c>
       <c r="O246" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19472,7 +19429,12 @@
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -19508,7 +19470,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -19540,9 +19502,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N247" t="n">
-        <v>96</v>
-      </c>
       <c r="O247" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19550,7 +19509,12 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -19586,7 +19550,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -19618,9 +19582,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N248" t="n">
-        <v>92</v>
-      </c>
       <c r="O248" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19628,7 +19589,12 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -19664,7 +19630,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -19696,9 +19662,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N249" t="n">
-        <v>103</v>
-      </c>
       <c r="O249" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19706,7 +19669,12 @@
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -19742,7 +19710,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -19774,9 +19742,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N250" t="n">
-        <v>109</v>
-      </c>
       <c r="O250" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19784,7 +19749,12 @@
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -19820,7 +19790,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -19852,9 +19822,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N251" t="n">
-        <v>110</v>
-      </c>
       <c r="O251" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19862,7 +19829,12 @@
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -19898,7 +19870,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -19930,9 +19902,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N252" t="n">
-        <v>104</v>
-      </c>
       <c r="O252" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -19940,7 +19909,12 @@
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -19976,7 +19950,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -20008,9 +19982,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N253" t="n">
-        <v>113</v>
-      </c>
       <c r="O253" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20018,7 +19989,12 @@
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20030,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -20086,9 +20062,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N254" t="n">
-        <v>123</v>
-      </c>
       <c r="O254" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20096,7 +20069,12 @@
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -20132,7 +20110,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -20164,9 +20142,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N255" t="n">
-        <v>133</v>
-      </c>
       <c r="O255" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20174,7 +20149,12 @@
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -20210,7 +20190,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -20242,9 +20222,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N256" t="n">
-        <v>136</v>
-      </c>
       <c r="O256" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20252,7 +20229,12 @@
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -20288,7 +20270,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -20320,9 +20302,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N257" t="n">
-        <v>162</v>
-      </c>
       <c r="O257" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20330,7 +20309,12 @@
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -20366,7 +20350,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -20398,9 +20382,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N258" t="n">
-        <v>195</v>
-      </c>
       <c r="O258" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20408,7 +20389,12 @@
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -20444,7 +20430,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -20476,9 +20462,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N259" t="n">
-        <v>205</v>
-      </c>
       <c r="O259" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20486,7 +20469,12 @@
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -20522,7 +20510,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -20554,9 +20542,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N260" t="n">
-        <v>202</v>
-      </c>
       <c r="O260" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20564,7 +20549,12 @@
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -20600,7 +20590,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -20632,9 +20622,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N261" t="n">
-        <v>207</v>
-      </c>
       <c r="O261" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20642,7 +20629,12 @@
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -20678,7 +20670,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -20710,9 +20702,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N262" t="n">
-        <v>251</v>
-      </c>
       <c r="O262" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20720,7 +20709,12 @@
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -20756,7 +20750,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -20788,9 +20782,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N263" t="n">
-        <v>219</v>
-      </c>
       <c r="O263" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20798,7 +20789,12 @@
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20830,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -20866,9 +20862,6 @@
           <t>Mortalidad materna</t>
         </is>
       </c>
-      <c r="N264" t="n">
-        <v>227</v>
-      </c>
       <c r="O264" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -20876,7 +20869,12 @@
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -20912,7 +20910,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -20951,7 +20949,12 @@
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20990,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -21026,7 +21029,12 @@
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -21101,7 +21109,7 @@
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21176,7 +21184,7 @@
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21251,7 +21259,7 @@
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21326,7 +21334,7 @@
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21401,7 +21409,7 @@
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21476,7 +21484,7 @@
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21551,7 +21559,7 @@
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21626,7 +21634,7 @@
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21709,7 @@
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21776,7 +21784,7 @@
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21851,7 +21859,7 @@
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21926,7 +21934,7 @@
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22001,7 +22009,7 @@
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22076,7 +22084,7 @@
       </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22151,7 +22159,7 @@
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22226,7 +22234,7 @@
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22301,7 +22309,7 @@
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22376,7 +22384,7 @@
       </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22459,7 @@
       </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22526,7 +22534,7 @@
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22601,7 +22609,7 @@
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22676,7 +22684,7 @@
       </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22751,7 +22759,7 @@
       </c>
       <c r="P289" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22826,7 +22834,7 @@
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22901,7 +22909,7 @@
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22976,7 +22984,7 @@
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23051,7 +23059,7 @@
       </c>
       <c r="P293" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23126,7 +23134,7 @@
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23201,7 +23209,7 @@
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23276,7 +23284,7 @@
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23351,7 +23359,7 @@
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23426,7 +23434,7 @@
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23501,7 +23509,7 @@
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23576,7 +23584,7 @@
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23651,7 +23659,7 @@
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23726,7 +23734,7 @@
       </c>
       <c r="P302" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23801,7 +23809,7 @@
       </c>
       <c r="P303" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23876,7 +23884,7 @@
       </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23951,7 +23959,7 @@
       </c>
       <c r="P305" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24026,7 +24034,7 @@
       </c>
       <c r="P306" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24101,7 +24109,7 @@
       </c>
       <c r="P307" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24176,7 +24184,7 @@
       </c>
       <c r="P308" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24251,7 +24259,7 @@
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24326,7 +24334,7 @@
       </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24401,7 +24409,7 @@
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24476,7 +24484,7 @@
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24551,7 +24559,7 @@
       </c>
       <c r="P313" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24626,7 +24634,7 @@
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24701,7 +24709,7 @@
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24776,7 +24784,7 @@
       </c>
       <c r="P316" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24851,7 +24859,7 @@
       </c>
       <c r="P317" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24926,7 +24934,7 @@
       </c>
       <c r="P318" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25001,7 +25009,7 @@
       </c>
       <c r="P319" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25076,7 +25084,7 @@
       </c>
       <c r="P320" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25151,7 +25159,7 @@
       </c>
       <c r="P321" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25226,7 +25234,7 @@
       </c>
       <c r="P322" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25301,7 +25309,7 @@
       </c>
       <c r="P323" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25376,7 +25384,7 @@
       </c>
       <c r="P324" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25454,7 +25462,7 @@
       </c>
       <c r="P325" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25532,7 +25540,7 @@
       </c>
       <c r="P326" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25610,7 +25618,7 @@
       </c>
       <c r="P327" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25688,7 +25696,7 @@
       </c>
       <c r="P328" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25766,7 +25774,7 @@
       </c>
       <c r="P329" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25844,7 +25852,7 @@
       </c>
       <c r="P330" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25919,7 +25927,7 @@
       </c>
       <c r="P331" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25994,7 +26002,7 @@
       </c>
       <c r="P332" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -26069,7 +26077,7 @@
       </c>
       <c r="P333" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -26144,7 +26152,7 @@
       </c>
       <c r="P334" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -26219,7 +26227,7 @@
       </c>
       <c r="P335" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -26294,7 +26302,7 @@
       </c>
       <c r="P336" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -26369,7 +26377,7 @@
       </c>
       <c r="P337" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26452,7 @@
       </c>
       <c r="P338" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -26519,7 +26527,7 @@
       </c>
       <c r="P339" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -26594,7 +26602,7 @@
       </c>
       <c r="P340" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -26669,7 +26677,7 @@
       </c>
       <c r="P341" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -26744,7 +26752,7 @@
       </c>
       <c r="P342" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -26819,7 +26827,7 @@
       </c>
       <c r="P343" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -26894,7 +26902,7 @@
       </c>
       <c r="P344" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -26969,7 +26977,7 @@
       </c>
       <c r="P345" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -27044,7 +27052,7 @@
       </c>
       <c r="P346" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -27119,7 +27127,7 @@
       </c>
       <c r="P347" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27202,7 @@
       </c>
       <c r="P348" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -27269,7 +27277,7 @@
       </c>
       <c r="P349" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -27344,7 +27352,7 @@
       </c>
       <c r="P350" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -27419,7 +27427,7 @@
       </c>
       <c r="P351" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -27494,7 +27502,7 @@
       </c>
       <c r="P352" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -27569,7 +27577,7 @@
       </c>
       <c r="P353" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -27644,7 +27652,7 @@
       </c>
       <c r="P354" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -27719,7 +27727,7 @@
       </c>
       <c r="P355" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -27794,7 +27802,7 @@
       </c>
       <c r="P356" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -27869,7 +27877,7 @@
       </c>
       <c r="P357" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -27944,7 +27952,7 @@
       </c>
       <c r="P358" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -28019,7 +28027,7 @@
       </c>
       <c r="P359" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -28094,7 +28102,7 @@
       </c>
       <c r="P360" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -28169,7 +28177,7 @@
       </c>
       <c r="P361" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -28244,7 +28252,7 @@
       </c>
       <c r="P362" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -28319,7 +28327,7 @@
       </c>
       <c r="P363" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28402,7 @@
       </c>
       <c r="P364" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -28469,7 +28477,7 @@
       </c>
       <c r="P365" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -28544,7 +28552,7 @@
       </c>
       <c r="P366" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -28619,7 +28627,7 @@
       </c>
       <c r="P367" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -28694,7 +28702,7 @@
       </c>
       <c r="P368" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -28769,7 +28777,7 @@
       </c>
       <c r="P369" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -28844,7 +28852,7 @@
       </c>
       <c r="P370" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -28919,7 +28927,7 @@
       </c>
       <c r="P371" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -28994,7 +29002,7 @@
       </c>
       <c r="P372" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -29069,7 +29077,7 @@
       </c>
       <c r="P373" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -29144,7 +29152,7 @@
       </c>
       <c r="P374" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -29219,7 +29227,7 @@
       </c>
       <c r="P375" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29302,7 @@
       </c>
       <c r="P376" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -29369,7 +29377,7 @@
       </c>
       <c r="P377" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -29444,7 +29452,7 @@
       </c>
       <c r="P378" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -29519,7 +29527,7 @@
       </c>
       <c r="P379" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -29594,7 +29602,7 @@
       </c>
       <c r="P380" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -29669,7 +29677,7 @@
       </c>
       <c r="P381" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -29744,7 +29752,7 @@
       </c>
       <c r="P382" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -29819,7 +29827,7 @@
       </c>
       <c r="P383" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -29894,7 +29902,7 @@
       </c>
       <c r="P384" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -29969,7 +29977,7 @@
       </c>
       <c r="P385" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -30044,7 +30052,7 @@
       </c>
       <c r="P386" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -30119,7 +30127,7 @@
       </c>
       <c r="P387" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -30194,7 +30202,7 @@
       </c>
       <c r="P388" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -30269,7 +30277,7 @@
       </c>
       <c r="P389" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -30344,7 +30352,7 @@
       </c>
       <c r="P390" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -30422,7 +30430,7 @@
       </c>
       <c r="P391" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -30500,7 +30508,7 @@
       </c>
       <c r="P392" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -30578,7 +30586,7 @@
       </c>
       <c r="P393" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -30656,7 +30664,7 @@
       </c>
       <c r="P394" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -30734,7 +30742,7 @@
       </c>
       <c r="P395" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -30812,7 +30820,7 @@
       </c>
       <c r="P396" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -30887,7 +30895,7 @@
       </c>
       <c r="P397" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -30962,7 +30970,7 @@
       </c>
       <c r="P398" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -31040,7 +31048,7 @@
       </c>
       <c r="P399" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -31118,7 +31126,7 @@
       </c>
       <c r="P400" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -31196,7 +31204,7 @@
       </c>
       <c r="P401" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -31274,7 +31282,7 @@
       </c>
       <c r="P402" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -31352,7 +31360,7 @@
       </c>
       <c r="P403" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -31430,7 +31438,7 @@
       </c>
       <c r="P404" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -31508,7 +31516,7 @@
       </c>
       <c r="P405" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -31586,7 +31594,7 @@
       </c>
       <c r="P406" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -31664,7 +31672,7 @@
       </c>
       <c r="P407" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -31742,7 +31750,7 @@
       </c>
       <c r="P408" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -31820,7 +31828,7 @@
       </c>
       <c r="P409" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -31898,7 +31906,7 @@
       </c>
       <c r="P410" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -31976,7 +31984,7 @@
       </c>
       <c r="P411" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -32054,7 +32062,7 @@
       </c>
       <c r="P412" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -32132,7 +32140,7 @@
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -32210,7 +32218,7 @@
       </c>
       <c r="P414" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -32288,7 +32296,7 @@
       </c>
       <c r="P415" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -32366,7 +32374,7 @@
       </c>
       <c r="P416" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -32444,7 +32452,7 @@
       </c>
       <c r="P417" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -32522,7 +32530,7 @@
       </c>
       <c r="P418" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -32600,7 +32608,7 @@
       </c>
       <c r="P419" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -32678,7 +32686,7 @@
       </c>
       <c r="P420" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -32756,7 +32764,7 @@
       </c>
       <c r="P421" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -32834,7 +32842,7 @@
       </c>
       <c r="P422" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -32912,7 +32920,7 @@
       </c>
       <c r="P423" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -32990,7 +32998,7 @@
       </c>
       <c r="P424" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -33068,7 +33076,7 @@
       </c>
       <c r="P425" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -33146,7 +33154,7 @@
       </c>
       <c r="P426" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -33224,7 +33232,7 @@
       </c>
       <c r="P427" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -33302,7 +33310,7 @@
       </c>
       <c r="P428" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -33380,7 +33388,7 @@
       </c>
       <c r="P429" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -33458,7 +33466,7 @@
       </c>
       <c r="P430" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -33536,7 +33544,7 @@
       </c>
       <c r="P431" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -33614,7 +33622,7 @@
       </c>
       <c r="P432" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -33692,7 +33700,7 @@
       </c>
       <c r="P433" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -33770,7 +33778,7 @@
       </c>
       <c r="P434" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -33848,7 +33856,7 @@
       </c>
       <c r="P435" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -33926,7 +33934,7 @@
       </c>
       <c r="P436" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -34004,7 +34012,7 @@
       </c>
       <c r="P437" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -34082,7 +34090,7 @@
       </c>
       <c r="P438" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -34160,7 +34168,7 @@
       </c>
       <c r="P439" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -34238,7 +34246,7 @@
       </c>
       <c r="P440" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -34316,7 +34324,7 @@
       </c>
       <c r="P441" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -34394,7 +34402,7 @@
       </c>
       <c r="P442" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -34472,7 +34480,7 @@
       </c>
       <c r="P443" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -34550,7 +34558,7 @@
       </c>
       <c r="P444" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -34628,7 +34636,7 @@
       </c>
       <c r="P445" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -34706,7 +34714,7 @@
       </c>
       <c r="P446" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -34784,7 +34792,7 @@
       </c>
       <c r="P447" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -34862,7 +34870,7 @@
       </c>
       <c r="P448" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -34940,7 +34948,7 @@
       </c>
       <c r="P449" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -35018,7 +35026,7 @@
       </c>
       <c r="P450" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -35096,7 +35104,7 @@
       </c>
       <c r="P451" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -35174,7 +35182,7 @@
       </c>
       <c r="P452" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -35252,7 +35260,7 @@
       </c>
       <c r="P453" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -35330,7 +35338,7 @@
       </c>
       <c r="P454" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -35408,7 +35416,7 @@
       </c>
       <c r="P455" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -35486,7 +35494,7 @@
       </c>
       <c r="P456" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -35564,7 +35572,7 @@
       </c>
       <c r="P457" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -35642,7 +35650,7 @@
       </c>
       <c r="P458" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -35720,7 +35728,7 @@
       </c>
       <c r="P459" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -35798,7 +35806,7 @@
       </c>
       <c r="P460" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -35876,7 +35884,7 @@
       </c>
       <c r="P461" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -35954,7 +35962,7 @@
       </c>
       <c r="P462" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -36032,7 +36040,7 @@
       </c>
       <c r="P463" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -36107,7 +36115,7 @@
       </c>
       <c r="P464" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -36157,7 +36165,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-es-ES]#,##0"/>
+    <numFmt numFmtId="165" formatCode="[$-es-ES]#,##0.00"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -69,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,6 +86,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -114,6 +123,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -144,6 +156,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -597,7 +612,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -630,7 +645,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="N7" s="8" t="n">
         <v>80.2</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -676,7 +691,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -709,7 +724,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="N8" s="8" t="n">
         <v>77.59999999999999</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
@@ -755,7 +770,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -788,7 +803,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="N9" s="8" t="n">
         <v>75.3</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -834,7 +849,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -867,7 +882,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N10" s="4" t="n">
+      <c r="N10" s="8" t="n">
         <v>73.3</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
@@ -913,7 +928,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -946,7 +961,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="N11" s="8" t="n">
         <v>71.59999999999999</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -992,7 +1007,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1025,7 +1040,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="N12" s="8" t="n">
         <v>70.2</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
@@ -1071,7 +1086,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1104,7 +1119,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N13" s="4" t="n">
+      <c r="N13" s="8" t="n">
         <v>68.8</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1150,7 +1165,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1183,7 +1198,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N14" s="4" t="n">
+      <c r="N14" s="8" t="n">
         <v>67.5</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
@@ -1229,7 +1244,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1262,7 +1277,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N15" s="4" t="n">
+      <c r="N15" s="8" t="n">
         <v>66.2</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1308,7 +1323,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1341,7 +1356,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N16" s="4" t="n">
+      <c r="N16" s="8" t="n">
         <v>64.7</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
@@ -1387,7 +1402,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1420,7 +1435,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N17" s="4" t="n">
+      <c r="N17" s="7" t="n">
         <v>63</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1466,7 +1481,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1499,7 +1514,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N18" s="4" t="n">
+      <c r="N18" s="8" t="n">
         <v>61.2</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
@@ -1545,7 +1560,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1578,7 +1593,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N19" s="4" t="n">
+      <c r="N19" s="8" t="n">
         <v>59.4</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -1624,7 +1639,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1657,7 +1672,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N20" s="4" t="n">
+      <c r="N20" s="8" t="n">
         <v>57.5</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
@@ -1703,7 +1718,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1736,7 +1751,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N21" s="4" t="n">
+      <c r="N21" s="8" t="n">
         <v>55.7</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -1782,7 +1797,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1815,7 +1830,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N22" s="4" t="n">
+      <c r="N22" s="8" t="n">
         <v>53.8</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
@@ -1861,7 +1876,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1894,7 +1909,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N23" s="4" t="n">
+      <c r="N23" s="7" t="n">
         <v>52</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -1940,7 +1955,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1973,7 +1988,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N24" s="4" t="n">
+      <c r="N24" s="7" t="n">
         <v>50</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
@@ -2019,7 +2034,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2052,7 +2067,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N25" s="4" t="n">
+      <c r="N25" s="8" t="n">
         <v>48.1</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -2098,7 +2113,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2131,7 +2146,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N26" s="4" t="n">
+      <c r="N26" s="8" t="n">
         <v>46.2</v>
       </c>
       <c r="O26" s="4" t="inlineStr">
@@ -2177,7 +2192,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2210,7 +2225,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N27" s="4" t="n">
+      <c r="N27" s="8" t="n">
         <v>44.2</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2256,7 +2271,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2289,7 +2304,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N28" s="4" t="n">
+      <c r="N28" s="8" t="n">
         <v>42.3</v>
       </c>
       <c r="O28" s="4" t="inlineStr">
@@ -2335,7 +2350,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2368,7 +2383,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N29" s="4" t="n">
+      <c r="N29" s="8" t="n">
         <v>40.6</v>
       </c>
       <c r="O29" s="4" t="inlineStr">
@@ -2414,7 +2429,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2447,7 +2462,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N30" s="4" t="n">
+      <c r="N30" s="7" t="n">
         <v>39</v>
       </c>
       <c r="O30" s="4" t="inlineStr">
@@ -2493,7 +2508,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2526,7 +2541,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N31" s="4" t="n">
+      <c r="N31" s="8" t="n">
         <v>37.6</v>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -2572,7 +2587,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2605,7 +2620,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N32" s="4" t="n">
+      <c r="N32" s="8" t="n">
         <v>36.3</v>
       </c>
       <c r="O32" s="4" t="inlineStr">
@@ -2651,7 +2666,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2684,7 +2699,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N33" s="4" t="n">
+      <c r="N33" s="7" t="n">
         <v>35</v>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -2730,7 +2745,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2763,7 +2778,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N34" s="4" t="n">
+      <c r="N34" s="8" t="n">
         <v>33.6</v>
       </c>
       <c r="O34" s="4" t="inlineStr">
@@ -2809,7 +2824,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2842,7 +2857,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N35" s="4" t="n">
+      <c r="N35" s="8" t="n">
         <v>32.2</v>
       </c>
       <c r="O35" s="4" t="inlineStr">
@@ -2888,7 +2903,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2921,7 +2936,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N36" s="4" t="n">
+      <c r="N36" s="8" t="n">
         <v>30.8</v>
       </c>
       <c r="O36" s="4" t="inlineStr">
@@ -2967,7 +2982,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -3000,7 +3015,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N37" s="4" t="n">
+      <c r="N37" s="8" t="n">
         <v>29.6</v>
       </c>
       <c r="O37" s="4" t="inlineStr">
@@ -3046,7 +3061,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -3079,7 +3094,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N38" s="4" t="n">
+      <c r="N38" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="O38" s="4" t="inlineStr">
@@ -3125,7 +3140,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -3158,7 +3173,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N39" s="4" t="n">
+      <c r="N39" s="8" t="n">
         <v>27.8</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -3204,7 +3219,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3237,7 +3252,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N40" s="4" t="n">
+      <c r="N40" s="8" t="n">
         <v>27.3</v>
       </c>
       <c r="O40" s="4" t="inlineStr">
@@ -3283,7 +3298,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3316,7 +3331,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N41" s="4" t="n">
+      <c r="N41" s="8" t="n">
         <v>26.8</v>
       </c>
       <c r="O41" s="4" t="inlineStr">
@@ -3362,7 +3377,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3395,7 +3410,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N42" s="4" t="n">
+      <c r="N42" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="O42" s="4" t="inlineStr">
@@ -3441,7 +3456,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3474,7 +3489,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N43" s="4" t="n">
+      <c r="N43" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="O43" s="4" t="inlineStr">
@@ -3520,7 +3535,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3553,7 +3568,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N44" s="4" t="n">
+      <c r="N44" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="O44" s="4" t="inlineStr">
@@ -3599,7 +3614,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G45" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3632,7 +3647,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N45" s="4" t="n">
+      <c r="N45" s="8" t="n">
         <v>23.4</v>
       </c>
       <c r="O45" s="4" t="inlineStr">
@@ -3678,7 +3693,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G46" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3711,7 +3726,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N46" s="4" t="n">
+      <c r="N46" s="8" t="n">
         <v>22.4</v>
       </c>
       <c r="O46" s="4" t="inlineStr">
@@ -3757,7 +3772,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="G47" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3790,7 +3805,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N47" s="4" t="n">
+      <c r="N47" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="O47" s="4" t="inlineStr">
@@ -3836,7 +3851,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="G48" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3869,7 +3884,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N48" s="4" t="n">
+      <c r="N48" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="O48" s="4" t="inlineStr">
@@ -3915,7 +3930,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="G49" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3948,7 +3963,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N49" s="4" t="n">
+      <c r="N49" s="8" t="n">
         <v>20.3</v>
       </c>
       <c r="O49" s="4" t="inlineStr">
@@ -3994,7 +4009,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -4027,7 +4042,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N50" s="4" t="n">
+      <c r="N50" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="O50" s="4" t="inlineStr">
@@ -4073,7 +4088,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -4106,7 +4121,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N51" s="4" t="n">
+      <c r="N51" s="8" t="n">
         <v>19.2</v>
       </c>
       <c r="O51" s="4" t="inlineStr">
@@ -4152,7 +4167,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4185,7 +4200,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N52" s="4" t="n">
+      <c r="N52" s="8" t="n">
         <v>18.5</v>
       </c>
       <c r="O52" s="4" t="inlineStr">
@@ -4231,7 +4246,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="G53" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4264,7 +4279,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N53" s="4" t="n">
+      <c r="N53" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="O53" s="4" t="inlineStr">
@@ -4310,7 +4325,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="G54" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4343,7 +4358,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N54" s="4" t="n">
+      <c r="N54" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="O54" s="4" t="inlineStr">
@@ -4389,7 +4404,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="G55" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4422,7 +4437,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N55" s="4" t="n">
+      <c r="N55" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="O55" s="4" t="inlineStr">
@@ -4468,7 +4483,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4501,7 +4516,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N56" s="4" t="n">
+      <c r="N56" s="8" t="n">
         <v>17.1</v>
       </c>
       <c r="O56" s="4" t="inlineStr">
@@ -4547,7 +4562,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4580,7 +4595,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N57" s="4" t="n">
+      <c r="N57" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="O57" s="4" t="inlineStr">
@@ -4626,7 +4641,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4659,7 +4674,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N58" s="4" t="n">
+      <c r="N58" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="O58" s="4" t="inlineStr">
@@ -4705,7 +4720,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="G59" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -4738,7 +4753,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N59" s="4" t="n">
+      <c r="N59" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="O59" s="4" t="inlineStr">
@@ -4784,7 +4799,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="G60" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -4817,7 +4832,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N60" s="4" t="n">
+      <c r="N60" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="O60" s="4" t="inlineStr">
@@ -4863,7 +4878,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="G61" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -4896,7 +4911,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N61" s="4" t="n">
+      <c r="N61" s="8" t="n">
         <v>18.3</v>
       </c>
       <c r="O61" s="4" t="inlineStr">
@@ -4942,7 +4957,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="G62" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -4975,7 +4990,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N62" s="4" t="n">
+      <c r="N62" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="O62" s="4" t="inlineStr">
@@ -5021,7 +5036,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="G63" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -5054,7 +5069,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N63" s="4" t="n">
+      <c r="N63" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="O63" s="4" t="inlineStr">
@@ -5100,7 +5115,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="G64" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -5133,7 +5148,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N64" s="4" t="n">
+      <c r="N64" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="O64" s="4" t="inlineStr">
@@ -5179,7 +5194,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="G65" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5212,7 +5227,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N65" s="4" t="n">
+      <c r="N65" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="O65" s="4" t="inlineStr">
@@ -5258,7 +5273,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="G66" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -5291,7 +5306,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N66" s="4" t="n">
+      <c r="N66" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="O66" s="4" t="inlineStr">
@@ -5337,7 +5352,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="G67" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -5370,7 +5385,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N67" s="4" t="n">
+      <c r="N67" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="O67" s="4" t="inlineStr">
@@ -5416,7 +5431,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="G68" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -5449,7 +5464,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N68" s="4" t="n">
+      <c r="N68" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="O68" s="4" t="inlineStr">
@@ -5495,7 +5510,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="G69" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -5528,7 +5543,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N69" s="4" t="n">
+      <c r="N69" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="O69" s="4" t="inlineStr">
@@ -5574,7 +5589,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="G70" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -5607,7 +5622,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N70" s="4" t="n">
+      <c r="N70" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="O70" s="4" t="inlineStr">
@@ -5653,7 +5668,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="G71" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -5686,7 +5701,7 @@
           <t>Mortalidad de menores de 5 años</t>
         </is>
       </c>
-      <c r="N71" s="4" t="n">
+      <c r="N71" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="O71" s="4" t="inlineStr">
@@ -5732,7 +5747,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="G72" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -5809,7 +5824,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -5886,7 +5901,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="G74" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -5963,7 +5978,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="G75" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -6040,7 +6055,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -6117,7 +6132,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="G77" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -6194,7 +6209,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="G78" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -6271,7 +6286,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="G79" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -6348,7 +6363,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="G80" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -6425,7 +6440,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G81" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -6502,7 +6517,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="G82" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -6579,7 +6594,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="G83" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -6656,7 +6671,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="G84" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -6733,7 +6748,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="G85" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -6810,7 +6825,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G86" s="4" t="n">
+      <c r="G86" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -6887,7 +6902,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="G87" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -6920,7 +6935,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N87" s="4" t="n">
+      <c r="N87" s="8" t="n">
         <v>0.342999994754791</v>
       </c>
       <c r="O87" s="4" t="inlineStr">
@@ -6966,7 +6981,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="G88" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -6999,7 +7014,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N88" s="4" t="n">
+      <c r="N88" s="8" t="n">
         <v>0.331499993801117</v>
       </c>
       <c r="O88" s="4" t="inlineStr">
@@ -7045,7 +7060,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G89" s="4" t="n">
+      <c r="G89" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -7078,7 +7093,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N89" s="4" t="n">
+      <c r="N89" s="8" t="n">
         <v>0.342900007963181</v>
       </c>
       <c r="O89" s="4" t="inlineStr">
@@ -7124,7 +7139,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G90" s="4" t="n">
+      <c r="G90" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -7201,7 +7216,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G91" s="4" t="n">
+      <c r="G91" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -7278,7 +7293,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G92" s="4" t="n">
+      <c r="G92" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -7355,7 +7370,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="G93" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -7388,7 +7403,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N93" s="4" t="n">
+      <c r="N93" s="8" t="n">
         <v>0.331900000572205</v>
       </c>
       <c r="O93" s="4" t="inlineStr">
@@ -7434,7 +7449,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="G94" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -7511,7 +7526,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G95" s="4" t="n">
+      <c r="G95" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -7544,7 +7559,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N95" s="4" t="n">
+      <c r="N95" s="8" t="n">
         <v>0.370400011539459</v>
       </c>
       <c r="O95" s="4" t="inlineStr">
@@ -7590,7 +7605,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G96" s="4" t="n">
+      <c r="G96" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -7623,7 +7638,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N96" s="4" t="n">
+      <c r="N96" s="8" t="n">
         <v>0.358200013637543</v>
       </c>
       <c r="O96" s="4" t="inlineStr">
@@ -7669,7 +7684,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G97" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -7702,7 +7717,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N97" s="4" t="n">
+      <c r="N97" s="8" t="n">
         <v>0.37279999256134</v>
       </c>
       <c r="O97" s="4" t="inlineStr">
@@ -7748,7 +7763,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G98" s="4" t="n">
+      <c r="G98" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -7781,7 +7796,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N98" s="4" t="n">
+      <c r="N98" s="8" t="n">
         <v>2.69309997558594</v>
       </c>
       <c r="O98" s="4" t="inlineStr">
@@ -7827,7 +7842,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G99" s="4" t="n">
+      <c r="G99" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -7860,7 +7875,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N99" s="4" t="n">
+      <c r="N99" s="8" t="n">
         <v>2.70009994506836</v>
       </c>
       <c r="O99" s="4" t="inlineStr">
@@ -7906,7 +7921,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G100" s="4" t="n">
+      <c r="G100" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -7939,7 +7954,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N100" s="4" t="n">
+      <c r="N100" s="8" t="n">
         <v>2.59829998016357</v>
       </c>
       <c r="O100" s="4" t="inlineStr">
@@ -7985,7 +8000,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G101" s="4" t="n">
+      <c r="G101" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -8018,7 +8033,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N101" s="4" t="n">
+      <c r="N101" s="8" t="n">
         <v>2.49959993362427</v>
       </c>
       <c r="O101" s="4" t="inlineStr">
@@ -8064,7 +8079,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G102" s="4" t="n">
+      <c r="G102" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -8141,7 +8156,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G103" s="4" t="n">
+      <c r="G103" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -8174,7 +8189,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N103" s="4" t="n">
+      <c r="N103" s="8" t="n">
         <v>2.6779000759</v>
       </c>
       <c r="O103" s="4" t="inlineStr">
@@ -8220,7 +8235,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G104" s="4" t="n">
+      <c r="G104" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -8253,7 +8268,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N104" s="4" t="n">
+      <c r="N104" s="8" t="n">
         <v>2.6775999069</v>
       </c>
       <c r="O104" s="4" t="inlineStr">
@@ -8299,7 +8314,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G105" s="4" t="n">
+      <c r="G105" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -8332,7 +8347,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N105" s="4" t="n">
+      <c r="N105" s="8" t="n">
         <v>2.5729999542</v>
       </c>
       <c r="O105" s="4" t="inlineStr">
@@ -8378,7 +8393,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G106" s="4" t="n">
+      <c r="G106" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -8411,7 +8426,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N106" s="4" t="n">
+      <c r="N106" s="8" t="n">
         <v>2.5999999046</v>
       </c>
       <c r="O106" s="4" t="inlineStr">
@@ -8457,7 +8472,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G107" s="4" t="n">
+      <c r="G107" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -8534,7 +8549,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G108" s="4" t="n">
+      <c r="G108" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -8611,7 +8626,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G109" s="4" t="n">
+      <c r="G109" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -8644,7 +8659,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N109" s="4" t="n">
+      <c r="N109" s="8" t="n">
         <v>1.4700000286</v>
       </c>
       <c r="O109" s="4" t="inlineStr">
@@ -8690,7 +8705,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G110" s="4" t="n">
+      <c r="G110" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -8767,7 +8782,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G111" s="4" t="n">
+      <c r="G111" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -8844,7 +8859,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G112" s="4" t="n">
+      <c r="G112" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -8921,7 +8936,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G113" s="4" t="n">
+      <c r="G113" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -8998,7 +9013,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G114" s="4" t="n">
+      <c r="G114" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -9075,7 +9090,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G115" s="4" t="n">
+      <c r="G115" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -9152,7 +9167,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G116" s="4" t="n">
+      <c r="G116" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -9229,7 +9244,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G117" s="4" t="n">
+      <c r="G117" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -9306,7 +9321,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G118" s="4" t="n">
+      <c r="G118" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -9383,7 +9398,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G119" s="4" t="n">
+      <c r="G119" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -9460,7 +9475,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G120" s="4" t="n">
+      <c r="G120" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -9537,7 +9552,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G121" s="4" t="n">
+      <c r="G121" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -9614,7 +9629,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G122" s="4" t="n">
+      <c r="G122" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
@@ -9691,7 +9706,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G123" s="4" t="n">
+      <c r="G123" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
@@ -9768,7 +9783,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G124" s="4" t="n">
+      <c r="G124" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -9801,7 +9816,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N124" s="4" t="n">
+      <c r="N124" s="8" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="O124" s="4" t="inlineStr">
@@ -9847,7 +9862,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G125" s="4" t="n">
+      <c r="G125" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -9924,7 +9939,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G126" s="4" t="n">
+      <c r="G126" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -10001,7 +10016,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G127" s="4" t="n">
+      <c r="G127" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -10034,7 +10049,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N127" s="4" t="n">
+      <c r="N127" s="8" t="n">
         <v>0.79</v>
       </c>
       <c r="O127" s="4" t="inlineStr">
@@ -10080,7 +10095,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G128" s="4" t="n">
+      <c r="G128" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -10113,7 +10128,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N128" s="4" t="n">
+      <c r="N128" s="8" t="n">
         <v>0.75</v>
       </c>
       <c r="O128" s="4" t="inlineStr">
@@ -10159,7 +10174,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G129" s="4" t="n">
+      <c r="G129" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -10192,7 +10207,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N129" s="4" t="n">
+      <c r="N129" s="8" t="n">
         <v>0.88</v>
       </c>
       <c r="O129" s="4" t="inlineStr">
@@ -10238,7 +10253,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G130" s="4" t="n">
+      <c r="G130" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -10271,7 +10286,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N130" s="4" t="n">
+      <c r="N130" s="8" t="n">
         <v>0.91</v>
       </c>
       <c r="O130" s="4" t="inlineStr">
@@ -10317,7 +10332,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G131" s="4" t="n">
+      <c r="G131" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -10350,7 +10365,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N131" s="4" t="n">
+      <c r="N131" s="8" t="n">
         <v>1.09</v>
       </c>
       <c r="O131" s="4" t="inlineStr">
@@ -10396,7 +10411,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G132" s="4" t="n">
+      <c r="G132" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -10429,7 +10444,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N132" s="4" t="n">
+      <c r="N132" s="8" t="n">
         <v>0.93</v>
       </c>
       <c r="O132" s="4" t="inlineStr">
@@ -10475,7 +10490,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G133" s="4" t="n">
+      <c r="G133" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
@@ -10508,7 +10523,7 @@
           <t>Camas hospitalarias por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N133" s="4" t="n">
+      <c r="N133" s="8" t="n">
         <v>0.99</v>
       </c>
       <c r="O133" s="4" t="inlineStr">
@@ -10554,7 +10569,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G134" s="4" t="n">
+      <c r="G134" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -10631,7 +10646,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G135" s="4" t="n">
+      <c r="G135" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -10708,7 +10723,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G136" s="4" t="n">
+      <c r="G136" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -10785,7 +10800,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G137" s="4" t="n">
+      <c r="G137" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
@@ -10862,7 +10877,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G138" s="4" t="n">
+      <c r="G138" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -10939,7 +10954,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G139" s="4" t="n">
+      <c r="G139" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -10972,7 +10987,7 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N139" s="4" t="n">
+      <c r="N139" s="8" t="n">
         <v>0.666</v>
       </c>
       <c r="O139" s="4" t="inlineStr">
@@ -11018,7 +11033,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G140" s="4" t="n">
+      <c r="G140" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
@@ -11095,7 +11110,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G141" s="4" t="n">
+      <c r="G141" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -11172,7 +11187,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G142" s="4" t="n">
+      <c r="G142" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -11249,7 +11264,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G143" s="4" t="n">
+      <c r="G143" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
@@ -11326,7 +11341,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G144" s="4" t="n">
+      <c r="G144" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
@@ -11359,7 +11374,7 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N144" s="4" t="n">
+      <c r="N144" s="8" t="n">
         <v>0.8149999999999999</v>
       </c>
       <c r="O144" s="4" t="inlineStr">
@@ -11405,7 +11420,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G145" s="4" t="n">
+      <c r="G145" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -11482,7 +11497,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G146" s="4" t="n">
+      <c r="G146" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -11559,7 +11574,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G147" s="4" t="n">
+      <c r="G147" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -11636,7 +11651,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G148" s="4" t="n">
+      <c r="G148" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -11713,7 +11728,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G149" s="4" t="n">
+      <c r="G149" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
@@ -11746,7 +11761,7 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N149" s="4" t="n">
+      <c r="N149" s="8" t="n">
         <v>0.883</v>
       </c>
       <c r="O149" s="4" t="inlineStr">
@@ -11792,7 +11807,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G150" s="4" t="n">
+      <c r="G150" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
@@ -11869,7 +11884,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G151" s="4" t="n">
+      <c r="G151" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
@@ -11946,7 +11961,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G152" s="4" t="n">
+      <c r="G152" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
@@ -12023,7 +12038,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G153" s="4" t="n">
+      <c r="G153" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
@@ -12056,7 +12071,7 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N153" s="4" t="n">
+      <c r="N153" s="8" t="n">
         <v>0.904</v>
       </c>
       <c r="O153" s="4" t="inlineStr">
@@ -12102,7 +12117,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G154" s="4" t="n">
+      <c r="G154" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
@@ -12135,7 +12150,7 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N154" s="4" t="n">
+      <c r="N154" s="8" t="n">
         <v>0.904</v>
       </c>
       <c r="O154" s="4" t="inlineStr">
@@ -12181,7 +12196,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G155" s="4" t="n">
+      <c r="G155" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
@@ -12214,7 +12229,7 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N155" s="4" t="n">
+      <c r="N155" s="8" t="n">
         <v>0.904</v>
       </c>
       <c r="O155" s="4" t="inlineStr">
@@ -12260,7 +12275,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G156" s="4" t="n">
+      <c r="G156" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
@@ -12337,7 +12352,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G157" s="4" t="n">
+      <c r="G157" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
@@ -12414,7 +12429,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G158" s="4" t="n">
+      <c r="G158" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
@@ -12491,7 +12506,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G159" s="4" t="n">
+      <c r="G159" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
@@ -12524,7 +12539,7 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N159" s="4" t="n">
+      <c r="N159" s="8" t="n">
         <v>0.83</v>
       </c>
       <c r="O159" s="4" t="inlineStr">
@@ -12570,7 +12585,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G160" s="4" t="n">
+      <c r="G160" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
@@ -12603,7 +12618,7 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N160" s="4" t="n">
+      <c r="N160" s="8" t="n">
         <v>0.996</v>
       </c>
       <c r="O160" s="4" t="inlineStr">
@@ -12649,7 +12664,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G161" s="4" t="n">
+      <c r="G161" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
@@ -12682,7 +12697,7 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N161" s="4" t="n">
+      <c r="N161" s="8" t="n">
         <v>0.833</v>
       </c>
       <c r="O161" s="4" t="inlineStr">
@@ -12728,7 +12743,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G162" s="4" t="n">
+      <c r="G162" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
@@ -12805,7 +12820,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G163" s="4" t="n">
+      <c r="G163" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -12838,7 +12853,7 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N163" s="4" t="n">
+      <c r="N163" s="8" t="n">
         <v>1.436</v>
       </c>
       <c r="O163" s="4" t="inlineStr">
@@ -12884,7 +12899,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G164" s="4" t="n">
+      <c r="G164" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -12917,7 +12932,7 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N164" s="4" t="n">
+      <c r="N164" s="8" t="n">
         <v>1.196</v>
       </c>
       <c r="O164" s="4" t="inlineStr">
@@ -12963,7 +12978,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G165" s="4" t="n">
+      <c r="G165" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
@@ -12996,7 +13011,7 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N165" s="4" t="n">
+      <c r="N165" s="8" t="n">
         <v>1.399</v>
       </c>
       <c r="O165" s="4" t="inlineStr">
@@ -13042,7 +13057,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G166" s="4" t="n">
+      <c r="G166" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -13075,7 +13090,7 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N166" s="4" t="n">
+      <c r="N166" s="8" t="n">
         <v>1.401</v>
       </c>
       <c r="O166" s="4" t="inlineStr">
@@ -13121,7 +13136,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G167" s="4" t="n">
+      <c r="G167" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
@@ -13154,7 +13169,7 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N167" s="4" t="n">
+      <c r="N167" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="O167" s="4" t="inlineStr">
@@ -13200,7 +13215,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G168" s="4" t="n">
+      <c r="G168" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -13233,7 +13248,7 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N168" s="4" t="n">
+      <c r="N168" s="8" t="n">
         <v>1.695</v>
       </c>
       <c r="O168" s="4" t="inlineStr">
@@ -13279,7 +13294,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G169" s="4" t="n">
+      <c r="G169" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -13312,7 +13327,7 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N169" s="4" t="n">
+      <c r="N169" s="8" t="n">
         <v>1.564</v>
       </c>
       <c r="O169" s="4" t="inlineStr">
@@ -13358,7 +13373,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G170" s="4" t="n">
+      <c r="G170" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -13435,7 +13450,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G171" s="4" t="n">
+      <c r="G171" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -13512,7 +13527,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G172" s="4" t="n">
+      <c r="G172" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
@@ -13589,7 +13604,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G173" s="4" t="n">
+      <c r="G173" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -13666,7 +13681,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G174" s="4" t="n">
+      <c r="G174" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -13699,7 +13714,7 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N174" s="4" t="n">
+      <c r="N174" s="8" t="n">
         <v>1.94</v>
       </c>
       <c r="O174" s="4" t="inlineStr">
@@ -13745,7 +13760,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G175" s="4" t="n">
+      <c r="G175" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
@@ -13822,7 +13837,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G176" s="4" t="n">
+      <c r="G176" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -13899,7 +13914,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G177" s="4" t="n">
+      <c r="G177" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
@@ -13976,7 +13991,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G178" s="4" t="n">
+      <c r="G178" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
@@ -14053,7 +14068,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G179" s="4" t="n">
+      <c r="G179" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -14130,7 +14145,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G180" s="4" t="n">
+      <c r="G180" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
@@ -14163,7 +14178,7 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N180" s="4" t="n">
+      <c r="N180" s="8" t="n">
         <v>1.922</v>
       </c>
       <c r="O180" s="4" t="inlineStr">
@@ -14209,7 +14224,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G181" s="4" t="n">
+      <c r="G181" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
@@ -14286,7 +14301,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G182" s="4" t="n">
+      <c r="G182" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -14363,7 +14378,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G183" s="4" t="n">
+      <c r="G183" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
@@ -14440,7 +14455,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G184" s="4" t="n">
+      <c r="G184" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
@@ -14517,7 +14532,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G185" s="4" t="n">
+      <c r="G185" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
@@ -14594,7 +14609,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G186" s="4" t="n">
+      <c r="G186" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
@@ -14671,7 +14686,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G187" s="4" t="n">
+      <c r="G187" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
@@ -14748,7 +14763,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G188" s="4" t="n">
+      <c r="G188" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
@@ -14825,7 +14840,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G189" s="4" t="n">
+      <c r="G189" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
@@ -14902,7 +14917,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G190" s="4" t="n">
+      <c r="G190" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
@@ -14979,7 +14994,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G191" s="4" t="n">
+      <c r="G191" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -15056,7 +15071,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G192" s="4" t="n">
+      <c r="G192" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -15133,7 +15148,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G193" s="4" t="n">
+      <c r="G193" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -15210,7 +15225,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G194" s="4" t="n">
+      <c r="G194" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
@@ -15287,7 +15302,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G195" s="4" t="n">
+      <c r="G195" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
@@ -15364,7 +15379,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G196" s="4" t="n">
+      <c r="G196" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
@@ -15397,7 +15412,7 @@
           <t>Médicos por cada 1.000 habitantes</t>
         </is>
       </c>
-      <c r="N196" s="4" t="n">
+      <c r="N196" s="8" t="n">
         <v>1.664</v>
       </c>
       <c r="O196" s="4" t="inlineStr">
@@ -15443,7 +15458,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G197" s="4" t="n">
+      <c r="G197" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
@@ -15520,7 +15535,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G198" s="4" t="n">
+      <c r="G198" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
@@ -15597,7 +15612,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G199" s="4" t="n">
+      <c r="G199" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
@@ -15674,7 +15689,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G200" s="4" t="n">
+      <c r="G200" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
@@ -15751,7 +15766,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G201" s="4" t="n">
+      <c r="G201" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
@@ -15828,7 +15843,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G202" s="4" t="n">
+      <c r="G202" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
@@ -15905,7 +15920,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G203" s="4" t="n">
+      <c r="G203" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
@@ -15982,7 +15997,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G204" s="4" t="n">
+      <c r="G204" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
@@ -16059,7 +16074,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G205" s="4" t="n">
+      <c r="G205" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
@@ -16140,7 +16155,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G206" s="4" t="n">
+      <c r="G206" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
@@ -16221,7 +16236,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G207" s="4" t="n">
+      <c r="G207" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
@@ -16302,7 +16317,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G208" s="4" t="n">
+      <c r="G208" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
@@ -16383,7 +16398,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G209" s="4" t="n">
+      <c r="G209" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
@@ -16464,7 +16479,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G210" s="4" t="n">
+      <c r="G210" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
@@ -16545,7 +16560,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G211" s="4" t="n">
+      <c r="G211" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
@@ -16626,7 +16641,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G212" s="4" t="n">
+      <c r="G212" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
@@ -16707,7 +16722,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G213" s="4" t="n">
+      <c r="G213" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
@@ -16788,7 +16803,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G214" s="4" t="n">
+      <c r="G214" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
@@ -16869,7 +16884,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G215" s="4" t="n">
+      <c r="G215" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
@@ -16950,7 +16965,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G216" s="4" t="n">
+      <c r="G216" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
@@ -17031,7 +17046,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G217" s="4" t="n">
+      <c r="G217" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
@@ -17112,7 +17127,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G218" s="4" t="n">
+      <c r="G218" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
@@ -17193,7 +17208,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G219" s="4" t="n">
+      <c r="G219" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
@@ -17274,7 +17289,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G220" s="4" t="n">
+      <c r="G220" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
@@ -17355,7 +17370,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G221" s="4" t="n">
+      <c r="G221" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
@@ -17436,7 +17451,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G222" s="4" t="n">
+      <c r="G222" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
@@ -17517,7 +17532,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G223" s="4" t="n">
+      <c r="G223" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
@@ -17598,7 +17613,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G224" s="4" t="n">
+      <c r="G224" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
@@ -17679,7 +17694,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G225" s="4" t="n">
+      <c r="G225" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
@@ -17760,7 +17775,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G226" s="4" t="n">
+      <c r="G226" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
@@ -17841,7 +17856,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G227" s="4" t="n">
+      <c r="G227" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
@@ -17922,7 +17937,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G228" s="4" t="n">
+      <c r="G228" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
@@ -18003,7 +18018,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G229" s="4" t="n">
+      <c r="G229" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
@@ -18084,7 +18099,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G230" s="4" t="n">
+      <c r="G230" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
@@ -18165,7 +18180,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G231" s="4" t="n">
+      <c r="G231" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
@@ -18246,7 +18261,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G232" s="4" t="n">
+      <c r="G232" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
@@ -18327,7 +18342,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G233" s="4" t="n">
+      <c r="G233" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
@@ -18408,7 +18423,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G234" s="4" t="n">
+      <c r="G234" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
@@ -18489,7 +18504,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G235" s="4" t="n">
+      <c r="G235" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
@@ -18570,7 +18585,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G236" s="4" t="n">
+      <c r="G236" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
@@ -18651,7 +18666,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G237" s="4" t="n">
+      <c r="G237" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
@@ -18732,7 +18747,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G238" s="4" t="n">
+      <c r="G238" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
@@ -18813,7 +18828,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G239" s="4" t="n">
+      <c r="G239" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
@@ -18894,7 +18909,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G240" s="4" t="n">
+      <c r="G240" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
@@ -18975,7 +18990,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G241" s="4" t="n">
+      <c r="G241" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
@@ -19056,7 +19071,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G242" s="4" t="n">
+      <c r="G242" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
@@ -19137,7 +19152,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G243" s="4" t="n">
+      <c r="G243" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
@@ -19218,7 +19233,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G244" s="4" t="n">
+      <c r="G244" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
@@ -19299,7 +19314,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G245" s="4" t="n">
+      <c r="G245" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
@@ -19380,7 +19395,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G246" s="4" t="n">
+      <c r="G246" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
@@ -19461,7 +19476,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G247" s="4" t="n">
+      <c r="G247" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
@@ -19542,7 +19557,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G248" s="4" t="n">
+      <c r="G248" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
@@ -19623,7 +19638,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G249" s="4" t="n">
+      <c r="G249" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
@@ -19704,7 +19719,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G250" s="4" t="n">
+      <c r="G250" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
@@ -19785,7 +19800,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G251" s="4" t="n">
+      <c r="G251" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
@@ -19866,7 +19881,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G252" s="4" t="n">
+      <c r="G252" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
@@ -19947,7 +19962,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G253" s="4" t="n">
+      <c r="G253" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
@@ -20028,7 +20043,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G254" s="4" t="n">
+      <c r="G254" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
@@ -20109,7 +20124,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G255" s="4" t="n">
+      <c r="G255" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
@@ -20190,7 +20205,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G256" s="4" t="n">
+      <c r="G256" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
@@ -20271,7 +20286,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G257" s="4" t="n">
+      <c r="G257" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
@@ -20352,7 +20367,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G258" s="4" t="n">
+      <c r="G258" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
@@ -20433,7 +20448,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G259" s="4" t="n">
+      <c r="G259" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
@@ -20514,7 +20529,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G260" s="4" t="n">
+      <c r="G260" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
@@ -20595,7 +20610,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G261" s="4" t="n">
+      <c r="G261" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
@@ -20676,7 +20691,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G262" s="4" t="n">
+      <c r="G262" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
@@ -20757,7 +20772,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G263" s="4" t="n">
+      <c r="G263" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
@@ -20838,7 +20853,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G264" s="4" t="n">
+      <c r="G264" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
@@ -20919,7 +20934,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G265" s="4" t="n">
+      <c r="G265" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
@@ -21000,7 +21015,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G266" s="4" t="n">
+      <c r="G266" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
@@ -21081,7 +21096,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G267" s="4" t="n">
+      <c r="G267" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
@@ -21162,7 +21177,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G268" s="4" t="n">
+      <c r="G268" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
@@ -21243,7 +21258,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G269" s="4" t="n">
+      <c r="G269" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
@@ -21324,7 +21339,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G270" s="4" t="n">
+      <c r="G270" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
@@ -21405,7 +21420,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G271" s="4" t="n">
+      <c r="G271" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
@@ -21486,7 +21501,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G272" s="4" t="n">
+      <c r="G272" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
@@ -21563,7 +21578,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G273" s="4" t="n">
+      <c r="G273" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
@@ -21640,7 +21655,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G274" s="4" t="n">
+      <c r="G274" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
@@ -21717,7 +21732,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G275" s="4" t="n">
+      <c r="G275" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
@@ -21794,7 +21809,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G276" s="4" t="n">
+      <c r="G276" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
@@ -21871,7 +21886,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G277" s="4" t="n">
+      <c r="G277" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
@@ -21948,7 +21963,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G278" s="4" t="n">
+      <c r="G278" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
@@ -22025,7 +22040,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G279" s="4" t="n">
+      <c r="G279" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
@@ -22102,7 +22117,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G280" s="4" t="n">
+      <c r="G280" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
@@ -22179,7 +22194,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G281" s="4" t="n">
+      <c r="G281" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
@@ -22256,7 +22271,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G282" s="4" t="n">
+      <c r="G282" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
@@ -22333,7 +22348,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G283" s="4" t="n">
+      <c r="G283" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
@@ -22410,7 +22425,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G284" s="4" t="n">
+      <c r="G284" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
@@ -22487,7 +22502,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G285" s="4" t="n">
+      <c r="G285" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
@@ -22564,7 +22579,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G286" s="4" t="n">
+      <c r="G286" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
@@ -22641,7 +22656,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G287" s="4" t="n">
+      <c r="G287" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
@@ -22718,7 +22733,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G288" s="4" t="n">
+      <c r="G288" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
@@ -22795,7 +22810,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G289" s="4" t="n">
+      <c r="G289" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
@@ -22872,7 +22887,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G290" s="4" t="n">
+      <c r="G290" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
@@ -22949,7 +22964,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G291" s="4" t="n">
+      <c r="G291" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
@@ -23026,7 +23041,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G292" s="4" t="n">
+      <c r="G292" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
@@ -23103,7 +23118,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G293" s="4" t="n">
+      <c r="G293" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
@@ -23180,7 +23195,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G294" s="4" t="n">
+      <c r="G294" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
@@ -23257,7 +23272,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G295" s="4" t="n">
+      <c r="G295" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
@@ -23334,7 +23349,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G296" s="4" t="n">
+      <c r="G296" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
@@ -23411,7 +23426,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G297" s="4" t="n">
+      <c r="G297" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
@@ -23488,7 +23503,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G298" s="4" t="n">
+      <c r="G298" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
@@ -23565,7 +23580,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G299" s="4" t="n">
+      <c r="G299" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
@@ -23642,7 +23657,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G300" s="4" t="n">
+      <c r="G300" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
@@ -23719,7 +23734,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G301" s="4" t="n">
+      <c r="G301" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
@@ -23796,7 +23811,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G302" s="4" t="n">
+      <c r="G302" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
@@ -23873,7 +23888,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G303" s="4" t="n">
+      <c r="G303" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
@@ -23950,7 +23965,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G304" s="4" t="n">
+      <c r="G304" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
@@ -24027,7 +24042,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G305" s="4" t="n">
+      <c r="G305" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
@@ -24104,7 +24119,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G306" s="4" t="n">
+      <c r="G306" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
@@ -24181,7 +24196,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G307" s="4" t="n">
+      <c r="G307" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
@@ -24258,7 +24273,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G308" s="4" t="n">
+      <c r="G308" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
@@ -24335,7 +24350,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G309" s="4" t="n">
+      <c r="G309" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
@@ -24412,7 +24427,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G310" s="4" t="n">
+      <c r="G310" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
@@ -24489,7 +24504,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G311" s="4" t="n">
+      <c r="G311" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
@@ -24566,7 +24581,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G312" s="4" t="n">
+      <c r="G312" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
@@ -24643,7 +24658,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G313" s="4" t="n">
+      <c r="G313" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
@@ -24720,7 +24735,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G314" s="4" t="n">
+      <c r="G314" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
@@ -24797,7 +24812,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G315" s="4" t="n">
+      <c r="G315" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
@@ -24874,7 +24889,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G316" s="4" t="n">
+      <c r="G316" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
@@ -24951,7 +24966,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G317" s="4" t="n">
+      <c r="G317" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
@@ -25028,7 +25043,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G318" s="4" t="n">
+      <c r="G318" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
@@ -25105,7 +25120,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G319" s="4" t="n">
+      <c r="G319" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
@@ -25182,7 +25197,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G320" s="4" t="n">
+      <c r="G320" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
@@ -25259,7 +25274,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G321" s="4" t="n">
+      <c r="G321" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
@@ -25336,7 +25351,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G322" s="4" t="n">
+      <c r="G322" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
@@ -25413,7 +25428,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G323" s="4" t="n">
+      <c r="G323" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
@@ -25490,7 +25505,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G324" s="4" t="n">
+      <c r="G324" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
@@ -25567,7 +25582,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G325" s="4" t="n">
+      <c r="G325" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
@@ -25644,7 +25659,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G326" s="4" t="n">
+      <c r="G326" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
@@ -25721,7 +25736,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G327" s="4" t="n">
+      <c r="G327" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
@@ -25798,7 +25813,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G328" s="4" t="n">
+      <c r="G328" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
@@ -25875,7 +25890,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G329" s="4" t="n">
+      <c r="G329" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
@@ -25952,7 +25967,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G330" s="4" t="n">
+      <c r="G330" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
@@ -25985,7 +26000,7 @@
           <t>Gasto corriente en salud como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N330" s="4" t="n">
+      <c r="N330" s="8" t="n">
         <v>2.41691327</v>
       </c>
       <c r="O330" s="4" t="inlineStr">
@@ -26031,7 +26046,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G331" s="4" t="n">
+      <c r="G331" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
@@ -26064,7 +26079,7 @@
           <t>Gasto corriente en salud como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N331" s="4" t="n">
+      <c r="N331" s="8" t="n">
         <v>2.18563724</v>
       </c>
       <c r="O331" s="4" t="inlineStr">
@@ -26110,7 +26125,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G332" s="4" t="n">
+      <c r="G332" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
@@ -26143,7 +26158,7 @@
           <t>Gasto corriente en salud como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N332" s="4" t="n">
+      <c r="N332" s="8" t="n">
         <v>4.11615133</v>
       </c>
       <c r="O332" s="4" t="inlineStr">
@@ -26189,7 +26204,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G333" s="4" t="n">
+      <c r="G333" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
@@ -26222,7 +26237,7 @@
           <t>Gasto corriente en salud como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N333" s="4" t="n">
+      <c r="N333" s="8" t="n">
         <v>4.1022191</v>
       </c>
       <c r="O333" s="4" t="inlineStr">
@@ -26268,7 +26283,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G334" s="4" t="n">
+      <c r="G334" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
@@ -26301,7 +26316,7 @@
           <t>Gasto corriente en salud como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N334" s="4" t="n">
+      <c r="N334" s="8" t="n">
         <v>4.55045986</v>
       </c>
       <c r="O334" s="4" t="inlineStr">
@@ -26347,7 +26362,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G335" s="4" t="n">
+      <c r="G335" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
@@ -26380,7 +26395,7 @@
           <t>Gasto corriente en salud como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N335" s="4" t="n">
+      <c r="N335" s="8" t="n">
         <v>3.77611423</v>
       </c>
       <c r="O335" s="4" t="inlineStr">
@@ -26426,7 +26441,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G336" s="4" t="n">
+      <c r="G336" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
@@ -26503,7 +26518,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G337" s="4" t="n">
+      <c r="G337" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H337" s="4" t="inlineStr">
@@ -26580,7 +26595,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G338" s="4" t="n">
+      <c r="G338" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H338" s="4" t="inlineStr">
@@ -26657,7 +26672,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G339" s="4" t="n">
+      <c r="G339" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H339" s="4" t="inlineStr">
@@ -26734,7 +26749,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G340" s="4" t="n">
+      <c r="G340" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H340" s="4" t="inlineStr">
@@ -26811,7 +26826,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G341" s="4" t="n">
+      <c r="G341" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H341" s="4" t="inlineStr">
@@ -26888,7 +26903,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G342" s="4" t="n">
+      <c r="G342" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H342" s="4" t="inlineStr">
@@ -26965,7 +26980,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G343" s="4" t="n">
+      <c r="G343" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H343" s="4" t="inlineStr">
@@ -27042,7 +27057,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G344" s="4" t="n">
+      <c r="G344" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H344" s="4" t="inlineStr">
@@ -27119,7 +27134,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G345" s="4" t="n">
+      <c r="G345" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H345" s="4" t="inlineStr">
@@ -27196,7 +27211,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G346" s="4" t="n">
+      <c r="G346" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H346" s="4" t="inlineStr">
@@ -27273,7 +27288,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G347" s="4" t="n">
+      <c r="G347" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H347" s="4" t="inlineStr">
@@ -27350,7 +27365,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G348" s="4" t="n">
+      <c r="G348" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H348" s="4" t="inlineStr">
@@ -27427,7 +27442,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G349" s="4" t="n">
+      <c r="G349" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H349" s="4" t="inlineStr">
@@ -27504,7 +27519,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G350" s="4" t="n">
+      <c r="G350" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H350" s="4" t="inlineStr">
@@ -27581,7 +27596,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G351" s="4" t="n">
+      <c r="G351" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H351" s="4" t="inlineStr">
@@ -27658,7 +27673,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G352" s="4" t="n">
+      <c r="G352" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H352" s="4" t="inlineStr">
@@ -27735,7 +27750,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G353" s="4" t="n">
+      <c r="G353" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H353" s="4" t="inlineStr">
@@ -27812,7 +27827,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G354" s="4" t="n">
+      <c r="G354" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H354" s="4" t="inlineStr">
@@ -27889,7 +27904,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G355" s="4" t="n">
+      <c r="G355" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H355" s="4" t="inlineStr">
@@ -27966,7 +27981,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G356" s="4" t="n">
+      <c r="G356" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H356" s="4" t="inlineStr">
@@ -28043,7 +28058,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G357" s="4" t="n">
+      <c r="G357" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H357" s="4" t="inlineStr">
@@ -28120,7 +28135,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G358" s="4" t="n">
+      <c r="G358" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H358" s="4" t="inlineStr">
@@ -28197,7 +28212,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G359" s="4" t="n">
+      <c r="G359" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H359" s="4" t="inlineStr">
@@ -28274,7 +28289,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G360" s="4" t="n">
+      <c r="G360" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H360" s="4" t="inlineStr">
@@ -28351,7 +28366,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G361" s="4" t="n">
+      <c r="G361" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H361" s="4" t="inlineStr">
@@ -28428,7 +28443,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G362" s="4" t="n">
+      <c r="G362" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H362" s="4" t="inlineStr">
@@ -28505,7 +28520,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G363" s="4" t="n">
+      <c r="G363" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H363" s="4" t="inlineStr">
@@ -28582,7 +28597,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G364" s="4" t="n">
+      <c r="G364" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H364" s="4" t="inlineStr">
@@ -28659,7 +28674,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G365" s="4" t="n">
+      <c r="G365" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H365" s="4" t="inlineStr">
@@ -28736,7 +28751,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G366" s="4" t="n">
+      <c r="G366" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H366" s="4" t="inlineStr">
@@ -28813,7 +28828,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G367" s="4" t="n">
+      <c r="G367" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H367" s="4" t="inlineStr">
@@ -28890,7 +28905,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G368" s="4" t="n">
+      <c r="G368" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H368" s="4" t="inlineStr">
@@ -28967,7 +28982,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G369" s="4" t="n">
+      <c r="G369" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H369" s="4" t="inlineStr">
@@ -29044,7 +29059,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G370" s="4" t="n">
+      <c r="G370" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H370" s="4" t="inlineStr">
@@ -29121,7 +29136,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G371" s="4" t="n">
+      <c r="G371" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H371" s="4" t="inlineStr">
@@ -29198,7 +29213,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G372" s="4" t="n">
+      <c r="G372" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H372" s="4" t="inlineStr">
@@ -29275,7 +29290,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G373" s="4" t="n">
+      <c r="G373" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H373" s="4" t="inlineStr">
@@ -29352,7 +29367,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G374" s="4" t="n">
+      <c r="G374" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H374" s="4" t="inlineStr">
@@ -29429,7 +29444,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G375" s="4" t="n">
+      <c r="G375" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H375" s="4" t="inlineStr">
@@ -29506,7 +29521,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G376" s="4" t="n">
+      <c r="G376" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H376" s="4" t="inlineStr">
@@ -29583,7 +29598,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G377" s="4" t="n">
+      <c r="G377" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H377" s="4" t="inlineStr">
@@ -29660,7 +29675,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G378" s="4" t="n">
+      <c r="G378" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H378" s="4" t="inlineStr">
@@ -29737,7 +29752,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G379" s="4" t="n">
+      <c r="G379" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H379" s="4" t="inlineStr">
@@ -29814,7 +29829,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G380" s="4" t="n">
+      <c r="G380" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H380" s="4" t="inlineStr">
@@ -29891,7 +29906,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G381" s="4" t="n">
+      <c r="G381" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H381" s="4" t="inlineStr">
@@ -29968,7 +29983,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G382" s="4" t="n">
+      <c r="G382" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H382" s="4" t="inlineStr">
@@ -30045,7 +30060,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G383" s="4" t="n">
+      <c r="G383" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H383" s="4" t="inlineStr">
@@ -30122,7 +30137,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G384" s="4" t="n">
+      <c r="G384" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H384" s="4" t="inlineStr">
@@ -30199,7 +30214,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G385" s="4" t="n">
+      <c r="G385" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H385" s="4" t="inlineStr">
@@ -30276,7 +30291,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G386" s="4" t="n">
+      <c r="G386" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H386" s="4" t="inlineStr">
@@ -30353,7 +30368,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G387" s="4" t="n">
+      <c r="G387" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H387" s="4" t="inlineStr">
@@ -30430,7 +30445,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G388" s="4" t="n">
+      <c r="G388" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H388" s="4" t="inlineStr">
@@ -30507,7 +30522,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G389" s="4" t="n">
+      <c r="G389" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H389" s="4" t="inlineStr">
@@ -30584,7 +30599,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G390" s="4" t="n">
+      <c r="G390" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H390" s="4" t="inlineStr">
@@ -30661,7 +30676,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G391" s="4" t="n">
+      <c r="G391" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H391" s="4" t="inlineStr">
@@ -30738,7 +30753,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G392" s="4" t="n">
+      <c r="G392" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H392" s="4" t="inlineStr">
@@ -30815,7 +30830,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G393" s="4" t="n">
+      <c r="G393" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H393" s="4" t="inlineStr">
@@ -30892,7 +30907,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G394" s="4" t="n">
+      <c r="G394" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H394" s="4" t="inlineStr">
@@ -30969,7 +30984,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G395" s="4" t="n">
+      <c r="G395" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H395" s="4" t="inlineStr">
@@ -31046,7 +31061,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G396" s="4" t="n">
+      <c r="G396" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H396" s="4" t="inlineStr">
@@ -31079,7 +31094,7 @@
           <t>Gasto corriente en salud per cápita</t>
         </is>
       </c>
-      <c r="N396" s="4" t="n">
+      <c r="N396" s="8" t="n">
         <v>164.68154907</v>
       </c>
       <c r="O396" s="4" t="inlineStr">
@@ -31125,7 +31140,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G397" s="4" t="n">
+      <c r="G397" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H397" s="4" t="inlineStr">
@@ -31158,7 +31173,7 @@
           <t>Gasto corriente en salud per cápita</t>
         </is>
       </c>
-      <c r="N397" s="4" t="n">
+      <c r="N397" s="8" t="n">
         <v>112.72974396</v>
       </c>
       <c r="O397" s="4" t="inlineStr">
@@ -31204,7 +31219,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G398" s="4" t="n">
+      <c r="G398" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H398" s="4" t="inlineStr">
@@ -31237,7 +31252,7 @@
           <t>Gasto corriente en salud per cápita</t>
         </is>
       </c>
-      <c r="N398" s="4" t="n">
+      <c r="N398" s="8" t="n">
         <v>153.21711731</v>
       </c>
       <c r="O398" s="4" t="inlineStr">
@@ -31283,7 +31298,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G399" s="4" t="n">
+      <c r="G399" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H399" s="4" t="inlineStr">
@@ -31316,7 +31331,7 @@
           <t>Gasto corriente en salud per cápita</t>
         </is>
       </c>
-      <c r="N399" s="4" t="n">
+      <c r="N399" s="8" t="n">
         <v>162.43952942</v>
       </c>
       <c r="O399" s="4" t="inlineStr">
@@ -31362,7 +31377,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G400" s="4" t="n">
+      <c r="G400" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H400" s="4" t="inlineStr">
@@ -31395,7 +31410,7 @@
           <t>Gasto corriente en salud per cápita</t>
         </is>
       </c>
-      <c r="N400" s="4" t="n">
+      <c r="N400" s="8" t="n">
         <v>208.66654968</v>
       </c>
       <c r="O400" s="4" t="inlineStr">
@@ -31441,7 +31456,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G401" s="4" t="n">
+      <c r="G401" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H401" s="4" t="inlineStr">
@@ -31474,7 +31489,7 @@
           <t>Gasto corriente en salud per cápita</t>
         </is>
       </c>
-      <c r="N401" s="4" t="n">
+      <c r="N401" s="8" t="n">
         <v>185.99124146</v>
       </c>
       <c r="O401" s="4" t="inlineStr">
@@ -31520,7 +31535,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G402" s="4" t="n">
+      <c r="G402" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H402" s="4" t="inlineStr">
@@ -31597,7 +31612,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G403" s="4" t="n">
+      <c r="G403" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H403" s="4" t="inlineStr">
@@ -31674,7 +31689,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G404" s="4" t="n">
+      <c r="G404" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H404" s="4" t="inlineStr">
@@ -31707,7 +31722,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N404" s="4" t="n">
+      <c r="N404" s="8" t="n">
         <v>58.6</v>
       </c>
       <c r="O404" s="4" t="inlineStr">
@@ -31753,7 +31768,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G405" s="4" t="n">
+      <c r="G405" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H405" s="4" t="inlineStr">
@@ -31786,7 +31801,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N405" s="4" t="n">
+      <c r="N405" s="8" t="n">
         <v>57.1</v>
       </c>
       <c r="O405" s="4" t="inlineStr">
@@ -31832,7 +31847,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G406" s="4" t="n">
+      <c r="G406" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H406" s="4" t="inlineStr">
@@ -31865,7 +31880,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N406" s="4" t="n">
+      <c r="N406" s="8" t="n">
         <v>55.9</v>
       </c>
       <c r="O406" s="4" t="inlineStr">
@@ -31911,7 +31926,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G407" s="4" t="n">
+      <c r="G407" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H407" s="4" t="inlineStr">
@@ -31944,7 +31959,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N407" s="4" t="n">
+      <c r="N407" s="8" t="n">
         <v>54.8</v>
       </c>
       <c r="O407" s="4" t="inlineStr">
@@ -31990,7 +32005,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G408" s="4" t="n">
+      <c r="G408" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H408" s="4" t="inlineStr">
@@ -32023,7 +32038,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N408" s="4" t="n">
+      <c r="N408" s="7" t="n">
         <v>54</v>
       </c>
       <c r="O408" s="4" t="inlineStr">
@@ -32069,7 +32084,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G409" s="4" t="n">
+      <c r="G409" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H409" s="4" t="inlineStr">
@@ -32102,7 +32117,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N409" s="4" t="n">
+      <c r="N409" s="8" t="n">
         <v>53.2</v>
       </c>
       <c r="O409" s="4" t="inlineStr">
@@ -32148,7 +32163,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G410" s="4" t="n">
+      <c r="G410" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H410" s="4" t="inlineStr">
@@ -32181,7 +32196,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N410" s="4" t="n">
+      <c r="N410" s="8" t="n">
         <v>52.6</v>
       </c>
       <c r="O410" s="4" t="inlineStr">
@@ -32227,7 +32242,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G411" s="4" t="n">
+      <c r="G411" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H411" s="4" t="inlineStr">
@@ -32260,7 +32275,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N411" s="4" t="n">
+      <c r="N411" s="8" t="n">
         <v>51.9</v>
       </c>
       <c r="O411" s="4" t="inlineStr">
@@ -32306,7 +32321,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G412" s="4" t="n">
+      <c r="G412" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H412" s="4" t="inlineStr">
@@ -32339,7 +32354,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N412" s="4" t="n">
+      <c r="N412" s="8" t="n">
         <v>51.2</v>
       </c>
       <c r="O412" s="4" t="inlineStr">
@@ -32385,7 +32400,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G413" s="4" t="n">
+      <c r="G413" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H413" s="4" t="inlineStr">
@@ -32418,7 +32433,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N413" s="4" t="n">
+      <c r="N413" s="8" t="n">
         <v>50.4</v>
       </c>
       <c r="O413" s="4" t="inlineStr">
@@ -32464,7 +32479,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G414" s="4" t="n">
+      <c r="G414" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H414" s="4" t="inlineStr">
@@ -32497,7 +32512,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N414" s="4" t="n">
+      <c r="N414" s="8" t="n">
         <v>49.3</v>
       </c>
       <c r="O414" s="4" t="inlineStr">
@@ -32543,7 +32558,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G415" s="4" t="n">
+      <c r="G415" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H415" s="4" t="inlineStr">
@@ -32576,7 +32591,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N415" s="4" t="n">
+      <c r="N415" s="8" t="n">
         <v>48.2</v>
       </c>
       <c r="O415" s="4" t="inlineStr">
@@ -32622,7 +32637,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G416" s="4" t="n">
+      <c r="G416" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H416" s="4" t="inlineStr">
@@ -32655,7 +32670,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N416" s="4" t="n">
+      <c r="N416" s="8" t="n">
         <v>46.9</v>
       </c>
       <c r="O416" s="4" t="inlineStr">
@@ -32701,7 +32716,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G417" s="4" t="n">
+      <c r="G417" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H417" s="4" t="inlineStr">
@@ -32734,7 +32749,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N417" s="4" t="n">
+      <c r="N417" s="8" t="n">
         <v>45.6</v>
       </c>
       <c r="O417" s="4" t="inlineStr">
@@ -32780,7 +32795,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G418" s="4" t="n">
+      <c r="G418" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H418" s="4" t="inlineStr">
@@ -32813,7 +32828,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N418" s="4" t="n">
+      <c r="N418" s="8" t="n">
         <v>44.4</v>
       </c>
       <c r="O418" s="4" t="inlineStr">
@@ -32859,7 +32874,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G419" s="4" t="n">
+      <c r="G419" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H419" s="4" t="inlineStr">
@@ -32892,7 +32907,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N419" s="4" t="n">
+      <c r="N419" s="8" t="n">
         <v>43.1</v>
       </c>
       <c r="O419" s="4" t="inlineStr">
@@ -32938,7 +32953,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G420" s="4" t="n">
+      <c r="G420" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H420" s="4" t="inlineStr">
@@ -32971,7 +32986,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N420" s="4" t="n">
+      <c r="N420" s="8" t="n">
         <v>41.7</v>
       </c>
       <c r="O420" s="4" t="inlineStr">
@@ -33017,7 +33032,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G421" s="4" t="n">
+      <c r="G421" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H421" s="4" t="inlineStr">
@@ -33050,7 +33065,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N421" s="4" t="n">
+      <c r="N421" s="8" t="n">
         <v>40.3</v>
       </c>
       <c r="O421" s="4" t="inlineStr">
@@ -33096,7 +33111,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G422" s="4" t="n">
+      <c r="G422" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H422" s="4" t="inlineStr">
@@ -33129,7 +33144,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N422" s="4" t="n">
+      <c r="N422" s="8" t="n">
         <v>38.9</v>
       </c>
       <c r="O422" s="4" t="inlineStr">
@@ -33175,7 +33190,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G423" s="4" t="n">
+      <c r="G423" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H423" s="4" t="inlineStr">
@@ -33208,7 +33223,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N423" s="4" t="n">
+      <c r="N423" s="8" t="n">
         <v>37.4</v>
       </c>
       <c r="O423" s="4" t="inlineStr">
@@ -33254,7 +33269,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G424" s="4" t="n">
+      <c r="G424" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H424" s="4" t="inlineStr">
@@ -33287,7 +33302,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N424" s="4" t="n">
+      <c r="N424" s="8" t="n">
         <v>35.9</v>
       </c>
       <c r="O424" s="4" t="inlineStr">
@@ -33333,7 +33348,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G425" s="4" t="n">
+      <c r="G425" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H425" s="4" t="inlineStr">
@@ -33366,7 +33381,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N425" s="4" t="n">
+      <c r="N425" s="8" t="n">
         <v>34.4</v>
       </c>
       <c r="O425" s="4" t="inlineStr">
@@ -33412,7 +33427,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G426" s="4" t="n">
+      <c r="G426" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H426" s="4" t="inlineStr">
@@ -33445,7 +33460,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N426" s="4" t="n">
+      <c r="N426" s="8" t="n">
         <v>33.1</v>
       </c>
       <c r="O426" s="4" t="inlineStr">
@@ -33491,7 +33506,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G427" s="4" t="n">
+      <c r="G427" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H427" s="4" t="inlineStr">
@@ -33524,7 +33539,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N427" s="4" t="n">
+      <c r="N427" s="8" t="n">
         <v>31.9</v>
       </c>
       <c r="O427" s="4" t="inlineStr">
@@ -33570,7 +33585,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G428" s="4" t="n">
+      <c r="G428" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H428" s="4" t="inlineStr">
@@ -33603,7 +33618,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N428" s="4" t="n">
+      <c r="N428" s="8" t="n">
         <v>30.8</v>
       </c>
       <c r="O428" s="4" t="inlineStr">
@@ -33649,7 +33664,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G429" s="4" t="n">
+      <c r="G429" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H429" s="4" t="inlineStr">
@@ -33682,7 +33697,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N429" s="4" t="n">
+      <c r="N429" s="8" t="n">
         <v>29.7</v>
       </c>
       <c r="O429" s="4" t="inlineStr">
@@ -33728,7 +33743,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G430" s="4" t="n">
+      <c r="G430" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H430" s="4" t="inlineStr">
@@ -33761,7 +33776,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N430" s="4" t="n">
+      <c r="N430" s="8" t="n">
         <v>28.7</v>
       </c>
       <c r="O430" s="4" t="inlineStr">
@@ -33807,7 +33822,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G431" s="4" t="n">
+      <c r="G431" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H431" s="4" t="inlineStr">
@@ -33840,7 +33855,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N431" s="4" t="n">
+      <c r="N431" s="8" t="n">
         <v>27.6</v>
       </c>
       <c r="O431" s="4" t="inlineStr">
@@ -33886,7 +33901,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G432" s="4" t="n">
+      <c r="G432" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H432" s="4" t="inlineStr">
@@ -33919,7 +33934,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N432" s="4" t="n">
+      <c r="N432" s="8" t="n">
         <v>26.5</v>
       </c>
       <c r="O432" s="4" t="inlineStr">
@@ -33965,7 +33980,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G433" s="4" t="n">
+      <c r="G433" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H433" s="4" t="inlineStr">
@@ -33998,7 +34013,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N433" s="4" t="n">
+      <c r="N433" s="8" t="n">
         <v>25.3</v>
       </c>
       <c r="O433" s="4" t="inlineStr">
@@ -34044,7 +34059,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G434" s="4" t="n">
+      <c r="G434" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H434" s="4" t="inlineStr">
@@ -34077,7 +34092,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N434" s="4" t="n">
+      <c r="N434" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="O434" s="4" t="inlineStr">
@@ -34123,7 +34138,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G435" s="4" t="n">
+      <c r="G435" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H435" s="4" t="inlineStr">
@@ -34156,7 +34171,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N435" s="4" t="n">
+      <c r="N435" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="O435" s="4" t="inlineStr">
@@ -34202,7 +34217,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G436" s="4" t="n">
+      <c r="G436" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H436" s="4" t="inlineStr">
@@ -34235,7 +34250,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N436" s="4" t="n">
+      <c r="N436" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="O436" s="4" t="inlineStr">
@@ -34281,7 +34296,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G437" s="4" t="n">
+      <c r="G437" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H437" s="4" t="inlineStr">
@@ -34314,7 +34329,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N437" s="4" t="n">
+      <c r="N437" s="8" t="n">
         <v>22.4</v>
       </c>
       <c r="O437" s="4" t="inlineStr">
@@ -34360,7 +34375,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G438" s="4" t="n">
+      <c r="G438" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H438" s="4" t="inlineStr">
@@ -34393,7 +34408,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N438" s="4" t="n">
+      <c r="N438" s="7" t="n">
         <v>22</v>
       </c>
       <c r="O438" s="4" t="inlineStr">
@@ -34439,7 +34454,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G439" s="4" t="n">
+      <c r="G439" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H439" s="4" t="inlineStr">
@@ -34472,7 +34487,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N439" s="4" t="n">
+      <c r="N439" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="O439" s="4" t="inlineStr">
@@ -34518,7 +34533,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G440" s="4" t="n">
+      <c r="G440" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H440" s="4" t="inlineStr">
@@ -34551,7 +34566,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N440" s="4" t="n">
+      <c r="N440" s="8" t="n">
         <v>20.8</v>
       </c>
       <c r="O440" s="4" t="inlineStr">
@@ -34597,7 +34612,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G441" s="4" t="n">
+      <c r="G441" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H441" s="4" t="inlineStr">
@@ -34630,7 +34645,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N441" s="4" t="n">
+      <c r="N441" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="O441" s="4" t="inlineStr">
@@ -34676,7 +34691,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G442" s="4" t="n">
+      <c r="G442" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H442" s="4" t="inlineStr">
@@ -34709,7 +34724,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N442" s="4" t="n">
+      <c r="N442" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="O442" s="4" t="inlineStr">
@@ -34755,7 +34770,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G443" s="4" t="n">
+      <c r="G443" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H443" s="4" t="inlineStr">
@@ -34788,7 +34803,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N443" s="4" t="n">
+      <c r="N443" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="O443" s="4" t="inlineStr">
@@ -34834,7 +34849,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G444" s="4" t="n">
+      <c r="G444" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H444" s="4" t="inlineStr">
@@ -34867,7 +34882,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N444" s="4" t="n">
+      <c r="N444" s="8" t="n">
         <v>17.5</v>
       </c>
       <c r="O444" s="4" t="inlineStr">
@@ -34913,7 +34928,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G445" s="4" t="n">
+      <c r="G445" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H445" s="4" t="inlineStr">
@@ -34946,7 +34961,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N445" s="4" t="n">
+      <c r="N445" s="7" t="n">
         <v>17</v>
       </c>
       <c r="O445" s="4" t="inlineStr">
@@ -34992,7 +35007,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G446" s="4" t="n">
+      <c r="G446" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H446" s="4" t="inlineStr">
@@ -35025,7 +35040,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N446" s="4" t="n">
+      <c r="N446" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="O446" s="4" t="inlineStr">
@@ -35071,7 +35086,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G447" s="4" t="n">
+      <c r="G447" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H447" s="4" t="inlineStr">
@@ -35104,7 +35119,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N447" s="4" t="n">
+      <c r="N447" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="O447" s="4" t="inlineStr">
@@ -35150,7 +35165,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G448" s="4" t="n">
+      <c r="G448" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H448" s="4" t="inlineStr">
@@ -35183,7 +35198,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N448" s="4" t="n">
+      <c r="N448" s="8" t="n">
         <v>15.7</v>
       </c>
       <c r="O448" s="4" t="inlineStr">
@@ -35229,7 +35244,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G449" s="4" t="n">
+      <c r="G449" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H449" s="4" t="inlineStr">
@@ -35262,7 +35277,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N449" s="4" t="n">
+      <c r="N449" s="8" t="n">
         <v>15.3</v>
       </c>
       <c r="O449" s="4" t="inlineStr">
@@ -35308,7 +35323,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G450" s="4" t="n">
+      <c r="G450" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H450" s="4" t="inlineStr">
@@ -35341,7 +35356,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N450" s="4" t="n">
+      <c r="N450" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="O450" s="4" t="inlineStr">
@@ -35387,7 +35402,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G451" s="4" t="n">
+      <c r="G451" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H451" s="4" t="inlineStr">
@@ -35420,7 +35435,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N451" s="4" t="n">
+      <c r="N451" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="O451" s="4" t="inlineStr">
@@ -35466,7 +35481,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G452" s="4" t="n">
+      <c r="G452" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H452" s="4" t="inlineStr">
@@ -35499,7 +35514,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N452" s="4" t="n">
+      <c r="N452" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="O452" s="4" t="inlineStr">
@@ -35545,7 +35560,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G453" s="4" t="n">
+      <c r="G453" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H453" s="4" t="inlineStr">
@@ -35578,7 +35593,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N453" s="4" t="n">
+      <c r="N453" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="O453" s="4" t="inlineStr">
@@ -35624,7 +35639,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G454" s="4" t="n">
+      <c r="G454" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H454" s="4" t="inlineStr">
@@ -35657,7 +35672,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N454" s="4" t="n">
+      <c r="N454" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="O454" s="4" t="inlineStr">
@@ -35703,7 +35718,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G455" s="4" t="n">
+      <c r="G455" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H455" s="4" t="inlineStr">
@@ -35736,7 +35751,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N455" s="4" t="n">
+      <c r="N455" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="O455" s="4" t="inlineStr">
@@ -35782,7 +35797,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G456" s="4" t="n">
+      <c r="G456" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H456" s="4" t="inlineStr">
@@ -35815,7 +35830,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N456" s="4" t="n">
+      <c r="N456" s="8" t="n">
         <v>15.1</v>
       </c>
       <c r="O456" s="4" t="inlineStr">
@@ -35861,7 +35876,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G457" s="4" t="n">
+      <c r="G457" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H457" s="4" t="inlineStr">
@@ -35894,7 +35909,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N457" s="4" t="n">
+      <c r="N457" s="8" t="n">
         <v>15.4</v>
       </c>
       <c r="O457" s="4" t="inlineStr">
@@ -35940,7 +35955,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G458" s="4" t="n">
+      <c r="G458" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H458" s="4" t="inlineStr">
@@ -35973,7 +35988,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N458" s="4" t="n">
+      <c r="N458" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="O458" s="4" t="inlineStr">
@@ -36019,7 +36034,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G459" s="4" t="n">
+      <c r="G459" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H459" s="4" t="inlineStr">
@@ -36052,7 +36067,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N459" s="4" t="n">
+      <c r="N459" s="8" t="n">
         <v>16.5</v>
       </c>
       <c r="O459" s="4" t="inlineStr">
@@ -36098,7 +36113,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G460" s="4" t="n">
+      <c r="G460" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H460" s="4" t="inlineStr">
@@ -36131,7 +36146,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N460" s="4" t="n">
+      <c r="N460" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="O460" s="4" t="inlineStr">
@@ -36177,7 +36192,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G461" s="4" t="n">
+      <c r="G461" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H461" s="4" t="inlineStr">
@@ -36210,7 +36225,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N461" s="4" t="n">
+      <c r="N461" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="O461" s="4" t="inlineStr">
@@ -36256,7 +36271,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G462" s="4" t="n">
+      <c r="G462" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H462" s="4" t="inlineStr">
@@ -36289,7 +36304,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N462" s="4" t="n">
+      <c r="N462" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="O462" s="4" t="inlineStr">
@@ -36335,7 +36350,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G463" s="4" t="n">
+      <c r="G463" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H463" s="4" t="inlineStr">
@@ -36368,7 +36383,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N463" s="4" t="n">
+      <c r="N463" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="O463" s="4" t="inlineStr">
@@ -36414,7 +36429,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G464" s="4" t="n">
+      <c r="G464" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H464" s="4" t="inlineStr">
@@ -36447,7 +36462,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N464" s="4" t="n">
+      <c r="N464" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="O464" s="4" t="inlineStr">
@@ -36493,7 +36508,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G465" s="4" t="n">
+      <c r="G465" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H465" s="4" t="inlineStr">
@@ -36526,7 +36541,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N465" s="4" t="n">
+      <c r="N465" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="O465" s="4" t="inlineStr">
@@ -36572,7 +36587,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G466" s="4" t="n">
+      <c r="G466" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H466" s="4" t="inlineStr">
@@ -36605,7 +36620,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N466" s="4" t="n">
+      <c r="N466" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="O466" s="4" t="inlineStr">
@@ -36651,7 +36666,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G467" s="4" t="n">
+      <c r="G467" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H467" s="4" t="inlineStr">
@@ -36684,7 +36699,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N467" s="4" t="n">
+      <c r="N467" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="O467" s="4" t="inlineStr">
@@ -36730,7 +36745,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G468" s="4" t="n">
+      <c r="G468" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H468" s="4" t="inlineStr">
@@ -36763,7 +36778,7 @@
           <t>Mortalidad infantil</t>
         </is>
       </c>
-      <c r="N468" s="4" t="n">
+      <c r="N468" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="O468" s="4" t="inlineStr">
@@ -36809,7 +36824,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G469" s="4" t="n">
+      <c r="G469" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H469" s="4" t="inlineStr">
@@ -36945,7 +36960,7 @@
           <t>Número de indicadores</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="7" t="n">
         <v>7</v>
       </c>
     </row>
@@ -36955,7 +36970,7 @@
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="7" t="n">
         <v>463</v>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9039,7 +9039,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11213,7 +11213,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11523,7 +11523,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11833,7 +11833,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13162,7 +13162,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13940,7 +13940,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14789,7 +14789,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15174,7 +15174,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15328,7 +15328,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15405,7 +15405,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15561,7 +15561,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15715,7 +15715,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15792,7 +15792,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15869,7 +15869,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16254,7 +16254,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16408,7 +16408,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16639,7 +16639,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16716,7 +16716,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16870,7 +16870,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16947,7 +16947,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17178,7 +17178,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17717,7 +17717,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17794,7 +17794,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17948,7 +17948,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18025,7 +18025,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18104,7 +18104,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18262,7 +18262,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18341,7 +18341,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18499,7 +18499,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18736,7 +18736,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18815,7 +18815,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18894,7 +18894,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18973,7 +18973,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19131,7 +19131,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19210,7 +19210,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20158,7 +20158,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20395,7 +20395,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20553,7 +20553,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20632,7 +20632,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20711,7 +20711,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20869,7 +20869,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20948,7 +20948,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21027,7 +21027,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21106,7 +21106,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21260,7 +21260,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21337,7 +21337,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21414,7 +21414,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21491,7 +21491,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21568,7 +21568,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21722,7 +21722,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21876,7 +21876,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21953,7 +21953,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22030,7 +22030,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22107,7 +22107,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22184,7 +22184,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22261,7 +22261,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22492,7 +22492,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22569,7 +22569,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22723,7 +22723,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22800,7 +22800,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22877,7 +22877,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22954,7 +22954,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23031,7 +23031,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23185,7 +23185,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23262,7 +23262,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23339,7 +23339,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23416,7 +23416,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23493,7 +23493,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23570,7 +23570,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23801,7 +23801,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23878,7 +23878,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23955,7 +23955,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24032,7 +24032,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24186,7 +24186,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24263,7 +24263,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24340,7 +24340,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24417,7 +24417,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24725,7 +24725,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24802,7 +24802,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25033,7 +25033,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25110,7 +25110,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25187,7 +25187,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25264,7 +25264,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25418,7 +25418,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25495,7 +25495,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25649,7 +25649,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25726,7 +25726,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25884,7 +25884,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25963,7 +25963,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26042,7 +26042,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26508,7 +26508,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26662,7 +26662,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26816,7 +26816,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26893,7 +26893,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26970,7 +26970,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27124,7 +27124,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27201,7 +27201,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27278,7 +27278,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27355,7 +27355,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27509,7 +27509,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27586,7 +27586,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27663,7 +27663,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27740,7 +27740,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27817,7 +27817,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -27971,7 +27971,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28048,7 +28048,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28125,7 +28125,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28202,7 +28202,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28279,7 +28279,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28356,7 +28356,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28433,7 +28433,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28510,7 +28510,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28587,7 +28587,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28664,7 +28664,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28741,7 +28741,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28818,7 +28818,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28895,7 +28895,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -28972,7 +28972,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29049,7 +29049,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29203,7 +29203,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29280,7 +29280,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29588,7 +29588,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29665,7 +29665,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29742,7 +29742,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29819,7 +29819,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -29973,7 +29973,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30050,7 +30050,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30204,7 +30204,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30281,7 +30281,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30358,7 +30358,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30435,7 +30435,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30512,7 +30512,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30589,7 +30589,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30666,7 +30666,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30743,7 +30743,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30820,7 +30820,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -30899,7 +30899,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -30978,7 +30978,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31057,7 +31057,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31215,7 +31215,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31294,7 +31294,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31371,7 +31371,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31448,7 +31448,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31606,7 +31606,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31685,7 +31685,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31764,7 +31764,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31843,7 +31843,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -31922,7 +31922,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32001,7 +32001,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32080,7 +32080,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32159,7 +32159,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32238,7 +32238,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32317,7 +32317,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32633,7 +32633,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32712,7 +32712,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32791,7 +32791,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -32949,7 +32949,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33107,7 +33107,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33186,7 +33186,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33265,7 +33265,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33344,7 +33344,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33423,7 +33423,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33581,7 +33581,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33660,7 +33660,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33739,7 +33739,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33818,7 +33818,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -33897,7 +33897,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -33976,7 +33976,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34055,7 +34055,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34134,7 +34134,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34213,7 +34213,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34292,7 +34292,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34450,7 +34450,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34529,7 +34529,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34687,7 +34687,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34766,7 +34766,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34845,7 +34845,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -34924,7 +34924,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35003,7 +35003,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35082,7 +35082,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35161,7 +35161,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35240,7 +35240,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35319,7 +35319,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35398,7 +35398,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35477,7 +35477,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35556,7 +35556,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35635,7 +35635,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35714,7 +35714,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35793,7 +35793,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -35872,7 +35872,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -35951,7 +35951,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36030,7 +36030,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36109,7 +36109,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36188,7 +36188,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36267,7 +36267,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36346,7 +36346,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36425,7 +36425,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36504,7 +36504,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36583,7 +36583,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36660,7 +36660,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36745,7 +36745,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9039,7 +9039,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11213,7 +11213,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11523,7 +11523,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11833,7 +11833,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13162,7 +13162,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13940,7 +13940,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14789,7 +14789,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15174,7 +15174,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15328,7 +15328,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15405,7 +15405,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15561,7 +15561,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15715,7 +15715,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15792,7 +15792,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15869,7 +15869,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16254,7 +16254,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16408,7 +16408,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16639,7 +16639,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16716,7 +16716,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16870,7 +16870,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16947,7 +16947,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17178,7 +17178,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17717,7 +17717,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17794,7 +17794,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17948,7 +17948,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18025,7 +18025,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18104,7 +18104,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18262,7 +18262,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18341,7 +18341,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18499,7 +18499,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18736,7 +18736,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18815,7 +18815,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18894,7 +18894,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18973,7 +18973,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19131,7 +19131,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19210,7 +19210,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20158,7 +20158,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20395,7 +20395,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20553,7 +20553,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20632,7 +20632,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20711,7 +20711,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20869,7 +20869,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20948,7 +20948,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21027,7 +21027,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21106,7 +21106,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21260,7 +21260,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21337,7 +21337,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21414,7 +21414,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21491,7 +21491,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21568,7 +21568,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21722,7 +21722,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21876,7 +21876,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21953,7 +21953,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22030,7 +22030,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22107,7 +22107,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22184,7 +22184,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22261,7 +22261,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22492,7 +22492,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22569,7 +22569,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22723,7 +22723,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22800,7 +22800,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22877,7 +22877,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22954,7 +22954,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23031,7 +23031,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23185,7 +23185,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23262,7 +23262,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23339,7 +23339,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23416,7 +23416,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23493,7 +23493,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23570,7 +23570,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23801,7 +23801,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23878,7 +23878,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23955,7 +23955,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24032,7 +24032,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24186,7 +24186,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24263,7 +24263,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24340,7 +24340,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24417,7 +24417,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24725,7 +24725,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24802,7 +24802,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25033,7 +25033,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25110,7 +25110,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25187,7 +25187,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25264,7 +25264,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25418,7 +25418,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25495,7 +25495,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25649,7 +25649,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25726,7 +25726,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25884,7 +25884,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25963,7 +25963,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26042,7 +26042,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26508,7 +26508,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26662,7 +26662,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26816,7 +26816,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26893,7 +26893,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26970,7 +26970,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27124,7 +27124,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27201,7 +27201,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27278,7 +27278,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27355,7 +27355,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27509,7 +27509,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27586,7 +27586,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27663,7 +27663,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27740,7 +27740,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27817,7 +27817,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -27971,7 +27971,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28048,7 +28048,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28125,7 +28125,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28202,7 +28202,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28279,7 +28279,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28356,7 +28356,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28433,7 +28433,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28510,7 +28510,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28587,7 +28587,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28664,7 +28664,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28741,7 +28741,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28818,7 +28818,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28895,7 +28895,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -28972,7 +28972,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29049,7 +29049,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29203,7 +29203,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29280,7 +29280,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29588,7 +29588,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29665,7 +29665,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29742,7 +29742,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29819,7 +29819,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -29973,7 +29973,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30050,7 +30050,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30204,7 +30204,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30281,7 +30281,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30358,7 +30358,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30435,7 +30435,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30512,7 +30512,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30589,7 +30589,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30666,7 +30666,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30743,7 +30743,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30820,7 +30820,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -30899,7 +30899,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -30978,7 +30978,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31057,7 +31057,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31215,7 +31215,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31294,7 +31294,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31371,7 +31371,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31448,7 +31448,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31606,7 +31606,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31685,7 +31685,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31764,7 +31764,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31843,7 +31843,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -31922,7 +31922,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32001,7 +32001,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32080,7 +32080,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32159,7 +32159,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32238,7 +32238,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32317,7 +32317,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32633,7 +32633,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32712,7 +32712,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32791,7 +32791,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -32949,7 +32949,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33107,7 +33107,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33186,7 +33186,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33265,7 +33265,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33344,7 +33344,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33423,7 +33423,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33581,7 +33581,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33660,7 +33660,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33739,7 +33739,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33818,7 +33818,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -33897,7 +33897,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -33976,7 +33976,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34055,7 +34055,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34134,7 +34134,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34213,7 +34213,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34292,7 +34292,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34450,7 +34450,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34529,7 +34529,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34687,7 +34687,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34766,7 +34766,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34845,7 +34845,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -34924,7 +34924,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35003,7 +35003,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35082,7 +35082,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35161,7 +35161,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35240,7 +35240,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35319,7 +35319,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35398,7 +35398,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35477,7 +35477,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35556,7 +35556,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35635,7 +35635,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35714,7 +35714,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35793,7 +35793,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -35872,7 +35872,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -35951,7 +35951,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36030,7 +36030,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36109,7 +36109,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36188,7 +36188,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36267,7 +36267,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36346,7 +36346,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36425,7 +36425,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36504,7 +36504,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36583,7 +36583,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36660,7 +36660,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36745,7 +36745,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9039,7 +9039,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11213,7 +11213,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11523,7 +11523,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11833,7 +11833,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13162,7 +13162,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13940,7 +13940,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14789,7 +14789,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15174,7 +15174,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15328,7 +15328,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15405,7 +15405,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15561,7 +15561,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15715,7 +15715,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15792,7 +15792,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15869,7 +15869,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16254,7 +16254,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16408,7 +16408,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16639,7 +16639,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16716,7 +16716,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16870,7 +16870,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16947,7 +16947,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17178,7 +17178,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17717,7 +17717,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17794,7 +17794,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17948,7 +17948,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18025,7 +18025,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18104,7 +18104,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18262,7 +18262,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18341,7 +18341,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18499,7 +18499,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18736,7 +18736,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18815,7 +18815,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18894,7 +18894,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18973,7 +18973,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19131,7 +19131,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19210,7 +19210,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20158,7 +20158,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20395,7 +20395,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20553,7 +20553,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20632,7 +20632,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20711,7 +20711,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20869,7 +20869,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20948,7 +20948,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21027,7 +21027,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21106,7 +21106,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21260,7 +21260,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21337,7 +21337,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21414,7 +21414,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21491,7 +21491,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21568,7 +21568,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21722,7 +21722,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21876,7 +21876,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21953,7 +21953,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22030,7 +22030,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22107,7 +22107,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22184,7 +22184,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22261,7 +22261,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22492,7 +22492,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22569,7 +22569,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22723,7 +22723,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22800,7 +22800,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22877,7 +22877,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22954,7 +22954,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23031,7 +23031,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23185,7 +23185,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23262,7 +23262,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23339,7 +23339,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23416,7 +23416,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23493,7 +23493,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23570,7 +23570,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23801,7 +23801,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23878,7 +23878,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23955,7 +23955,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24032,7 +24032,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24186,7 +24186,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24263,7 +24263,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24340,7 +24340,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24417,7 +24417,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24725,7 +24725,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24802,7 +24802,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25033,7 +25033,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25110,7 +25110,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25187,7 +25187,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25264,7 +25264,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25418,7 +25418,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25495,7 +25495,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25649,7 +25649,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25726,7 +25726,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25884,7 +25884,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25963,7 +25963,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26042,7 +26042,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26508,7 +26508,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26662,7 +26662,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26816,7 +26816,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26893,7 +26893,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26970,7 +26970,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27124,7 +27124,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27201,7 +27201,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27278,7 +27278,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27355,7 +27355,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27509,7 +27509,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27586,7 +27586,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27663,7 +27663,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27740,7 +27740,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27817,7 +27817,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -27971,7 +27971,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28048,7 +28048,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28125,7 +28125,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28202,7 +28202,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28279,7 +28279,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28356,7 +28356,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28433,7 +28433,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28510,7 +28510,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28587,7 +28587,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28664,7 +28664,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28741,7 +28741,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28818,7 +28818,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28895,7 +28895,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -28972,7 +28972,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29049,7 +29049,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29203,7 +29203,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29280,7 +29280,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29588,7 +29588,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29665,7 +29665,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29742,7 +29742,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29819,7 +29819,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -29973,7 +29973,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30050,7 +30050,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30204,7 +30204,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30281,7 +30281,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30358,7 +30358,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30435,7 +30435,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30512,7 +30512,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30589,7 +30589,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30666,7 +30666,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30743,7 +30743,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30820,7 +30820,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -30899,7 +30899,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -30978,7 +30978,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31057,7 +31057,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31215,7 +31215,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31294,7 +31294,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31371,7 +31371,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31448,7 +31448,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31606,7 +31606,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31685,7 +31685,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31764,7 +31764,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31843,7 +31843,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -31922,7 +31922,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32001,7 +32001,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32080,7 +32080,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32159,7 +32159,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32238,7 +32238,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32317,7 +32317,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32633,7 +32633,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32712,7 +32712,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32791,7 +32791,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -32949,7 +32949,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33107,7 +33107,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33186,7 +33186,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33265,7 +33265,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33344,7 +33344,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33423,7 +33423,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33581,7 +33581,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33660,7 +33660,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33739,7 +33739,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33818,7 +33818,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -33897,7 +33897,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -33976,7 +33976,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34055,7 +34055,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34134,7 +34134,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34213,7 +34213,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34292,7 +34292,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34450,7 +34450,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34529,7 +34529,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34687,7 +34687,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34766,7 +34766,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34845,7 +34845,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -34924,7 +34924,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35003,7 +35003,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35082,7 +35082,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35161,7 +35161,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35240,7 +35240,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35319,7 +35319,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35398,7 +35398,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35477,7 +35477,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35556,7 +35556,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35635,7 +35635,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35714,7 +35714,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35793,7 +35793,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -35872,7 +35872,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -35951,7 +35951,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36030,7 +36030,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36109,7 +36109,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36188,7 +36188,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36267,7 +36267,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36346,7 +36346,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36425,7 +36425,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36504,7 +36504,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36583,7 +36583,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36660,7 +36660,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36745,7 +36745,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
